--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,7446 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129895884</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>457831</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6677903</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre och lite färskare ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129906213</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>457973</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6678187</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129896799</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>457943</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6678103</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129895608</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>457684</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6678274</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129903410</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>457802</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6678361</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129896363</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>458038</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6677894</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129901093</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>457936</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6678130</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129903311</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>457721</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6678336</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129903889</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>458004</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6678076</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129906122</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>458021</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6678149</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129896298</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>458013</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6677834</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129905534</v>
+      </c>
+      <c r="B27" t="n">
+        <v>81066</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>458192</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6678014</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129903332</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>457738</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6678344</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129906012</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>458056</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6678145</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129903137</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>457711</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6678336</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129904258</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>458060</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6677965</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129895637</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>457691</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6678174</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129896809</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>457924</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6678115</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129895788</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>457819</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6677981</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129903495</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>457854</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6678241</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129905898</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>458188</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6678089</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129901643</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>457875</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6678186</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129896625</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>457943</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6678019</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129896559</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>457931</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6678011</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129896716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>457951</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6678037</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129901703</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>457857</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6678215</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129896531</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>457940</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6677971</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129905906</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>458187</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6678088</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129895810</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>457876</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6677971</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129895784</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>457792</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6677984</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129896481</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>457943</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6677968</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129903632</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>457937</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6678255</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Inte jätte färska. På tall.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129903770</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>457943</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6678120</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129901694</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>457867</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6678204</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Sparsamt ringhack på 2 tall.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129895622</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>457689</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6678248</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129906281</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>457937</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6678260</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129904261</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>458060</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6677965</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129904248</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>458070</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6677915</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129896461</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>457943</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6677964</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129895861</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92917</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>457867</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6677937</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129905893</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>458190</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6678079</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129903904</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>458009</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6678073</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129895750</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>457776</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6677988</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, en rad med sav.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129904077</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>458047</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6677984</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129896775</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>457962</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6678074</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129901759</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>457813</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6678274</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129895673</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>457806</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6678097</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129896652</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>457954</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6678018</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129906347</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>457859</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6678305</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129903802</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>457983</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6678105</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129903740</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>457907</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6678176</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129895677</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>457806</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6678096</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129895589</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>457678</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6678274</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129896274</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>458013</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6677833</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129896565</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>457928</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6678006</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129904132</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>458061</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6677989</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129901758</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>457814</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6678274</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129895801</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>457826</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6678001</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129900516</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>457915</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6678101</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129901768</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>457765</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6678299</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129901658</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>457862</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6678208</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129906105</v>
+      </c>
+      <c r="B77" t="n">
+        <v>88998</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>510</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>458040</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6678171</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129901597</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>457892</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6678150</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129896383</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>458001</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6677916</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129896578</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>457933</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6678030</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt. På granstam.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129895634</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>457704</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6678154</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129903924</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>458007</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6678050</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129895884</v>
+        <v>129906213</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,39 +2520,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457831</v>
+        <v>457973</v>
       </c>
       <c r="R16" t="n">
-        <v>6677903</v>
+        <v>6678187</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2584,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2594,12 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2626,7 +2616,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129906213</v>
+        <v>129903410</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2657,14 +2647,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457973</v>
+        <v>457802</v>
       </c>
       <c r="R17" t="n">
-        <v>6678187</v>
+        <v>6678361</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2696,7 +2686,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2706,7 +2696,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2845,7 +2835,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129895608</v>
+        <v>129895884</v>
       </c>
       <c r="B19" t="n">
         <v>57736</v>
@@ -2885,13 +2875,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457684</v>
+        <v>457831</v>
       </c>
       <c r="R19" t="n">
-        <v>6678274</v>
+        <v>6677903</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,7 +2910,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,12 +2920,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,10 +2952,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129903410</v>
+        <v>129895608</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,37 +2963,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457802</v>
+        <v>457684</v>
       </c>
       <c r="R20" t="n">
-        <v>6678361</v>
+        <v>6678274</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896363</v>
+        <v>129903311</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3100,19 +3100,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458038</v>
+        <v>457721</v>
       </c>
       <c r="R21" t="n">
-        <v>6677894</v>
+        <v>6678336</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,7 +3154,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,54 +3186,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129901093</v>
+        <v>129906122</v>
       </c>
       <c r="B22" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457936</v>
+        <v>458021</v>
       </c>
       <c r="R22" t="n">
-        <v>6678130</v>
+        <v>6678149</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3260,7 +3256,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3270,7 +3266,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3297,10 +3298,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129903311</v>
+        <v>129903889</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,39 +3309,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457721</v>
+        <v>458004</v>
       </c>
       <c r="R23" t="n">
-        <v>6678336</v>
+        <v>6678076</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3372,7 +3368,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3382,12 +3378,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,45 +3405,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129903889</v>
+        <v>129901093</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458004</v>
+        <v>457936</v>
       </c>
       <c r="R24" t="n">
-        <v>6678076</v>
+        <v>6678130</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,10 +3521,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129906122</v>
+        <v>129896298</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3532,37 +3532,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458021</v>
+        <v>458013</v>
       </c>
       <c r="R25" t="n">
-        <v>6678149</v>
+        <v>6677834</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3591,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3601,12 +3606,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,10 +3638,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129896298</v>
+        <v>129896363</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,16 +3649,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3673,13 +3678,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458013</v>
+        <v>458038</v>
       </c>
       <c r="R26" t="n">
-        <v>6677834</v>
+        <v>6677894</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3713,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3723,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129905534</v>
+        <v>129903137</v>
       </c>
       <c r="B27" t="n">
-        <v>81066</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,34 +3761,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458192</v>
+        <v>457711</v>
       </c>
       <c r="R27" t="n">
-        <v>6678014</v>
+        <v>6678336</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3862,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129903332</v>
+        <v>129905534</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,34 +3873,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457738</v>
+        <v>458192</v>
       </c>
       <c r="R28" t="n">
-        <v>6678344</v>
+        <v>6678014</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3932,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3942,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4071,10 +4076,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903137</v>
+        <v>129903332</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4082,21 +4087,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457711</v>
+        <v>457738</v>
       </c>
       <c r="R30" t="n">
-        <v>6678336</v>
+        <v>6678344</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4146,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,12 +4156,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4504,7 +4504,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R34" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129903495</v>
+        <v>129895788</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,37 +4632,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457854</v>
+        <v>457819</v>
       </c>
       <c r="R35" t="n">
-        <v>6678241</v>
+        <v>6677981</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4691,7 +4696,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4706,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4835,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129901643</v>
+        <v>129903495</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,39 +4856,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457875</v>
+        <v>457854</v>
       </c>
       <c r="R37" t="n">
-        <v>6678186</v>
+        <v>6678241</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4910,7 +4915,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4920,12 +4925,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5283,42 +5283,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B41" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5327,10 +5323,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R41" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5362,7 +5358,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5368,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,38 +5400,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>92881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R42" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,12 +5489,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129895784</v>
+        <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,39 +5746,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457792</v>
+        <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6677984</v>
+        <v>6678120</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5815,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5852,7 +5842,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129896481</v>
+        <v>129903632</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5883,19 +5873,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457943</v>
+        <v>457937</v>
       </c>
       <c r="R46" t="n">
-        <v>6677968</v>
+        <v>6678255</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5927,7 +5917,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5937,12 +5927,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5969,7 +5959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903632</v>
+        <v>129895784</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -6005,14 +5995,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457937</v>
+        <v>457792</v>
       </c>
       <c r="R47" t="n">
-        <v>6678255</v>
+        <v>6677984</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6044,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6054,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6086,10 +6076,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129903770</v>
+        <v>129896481</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6097,24 +6087,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6124,7 +6119,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6678120</v>
+        <v>6677968</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6156,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6166,7 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6544,7 +6544,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904261</v>
+        <v>129904248</v>
       </c>
       <c r="B52" t="n">
         <v>78838</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458060</v>
+        <v>458070</v>
       </c>
       <c r="R52" t="n">
-        <v>6677965</v>
+        <v>6677915</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6651,7 +6651,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129904248</v>
+        <v>129904261</v>
       </c>
       <c r="B53" t="n">
         <v>78838</v>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458070</v>
+        <v>458060</v>
       </c>
       <c r="R53" t="n">
-        <v>6677915</v>
+        <v>6677965</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129905893</v>
+        <v>129903904</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,34 +6997,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458190</v>
+        <v>458009</v>
       </c>
       <c r="R56" t="n">
-        <v>6678079</v>
+        <v>6678073</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7066,7 +7071,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7093,10 +7103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129903904</v>
+        <v>129905893</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7104,39 +7114,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458009</v>
+        <v>458190</v>
       </c>
       <c r="R57" t="n">
-        <v>6678073</v>
+        <v>6678079</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7168,7 +7173,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7178,12 +7183,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,39 +7338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R59" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7402,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7412,12 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7551,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7562,34 +7552,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R61" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7616,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7626,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,7 +7658,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129895673</v>
+        <v>129903802</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457806</v>
+        <v>457983</v>
       </c>
       <c r="R62" t="n">
-        <v>6678097</v>
+        <v>6678105</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129896652</v>
+        <v>129903740</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7776,39 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457954</v>
+        <v>457907</v>
       </c>
       <c r="R63" t="n">
-        <v>6678018</v>
+        <v>6678176</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7840,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7850,12 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7989,7 +7979,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903802</v>
+        <v>129895673</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -8024,13 +8014,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457983</v>
+        <v>457806</v>
       </c>
       <c r="R65" t="n">
-        <v>6678105</v>
+        <v>6678097</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,7 +8049,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8059,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129903740</v>
+        <v>129896652</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,34 +8097,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457907</v>
+        <v>457954</v>
       </c>
       <c r="R66" t="n">
-        <v>6678176</v>
+        <v>6678018</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8171,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8310,50 +8310,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895589</v>
+        <v>129896274</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R68" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8385,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8395,12 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,45 +8417,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129896274</v>
+        <v>129895578</v>
       </c>
       <c r="B69" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458013</v>
+        <v>457678</v>
       </c>
       <c r="R69" t="n">
-        <v>6677833</v>
+        <v>6678274</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8497,7 +8492,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,7 +8502,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8534,7 +8534,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129896565</v>
+        <v>129901758</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457928</v>
+        <v>457814</v>
       </c>
       <c r="R70" t="n">
-        <v>6678006</v>
+        <v>6678274</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129901758</v>
+        <v>129896565</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R72" t="n">
-        <v>6678274</v>
+        <v>6678006</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129895801</v>
+        <v>129900516</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457826</v>
+        <v>457915</v>
       </c>
       <c r="R73" t="n">
-        <v>6678001</v>
+        <v>6678101</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129900516</v>
+        <v>129901768</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457915</v>
+        <v>457765</v>
       </c>
       <c r="R74" t="n">
-        <v>6678101</v>
+        <v>6678299</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129901768</v>
+        <v>129895801</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457765</v>
+        <v>457826</v>
       </c>
       <c r="R75" t="n">
-        <v>6678299</v>
+        <v>6678001</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,54 +9176,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901658</v>
+        <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>92881</v>
+        <v>88998</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457862</v>
+        <v>458040</v>
       </c>
       <c r="R76" t="n">
-        <v>6678208</v>
+        <v>6678171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9255,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9265,7 +9256,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9292,10 +9283,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129906105</v>
+        <v>129901597</v>
       </c>
       <c r="B77" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9303,34 +9294,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458040</v>
+        <v>457892</v>
       </c>
       <c r="R77" t="n">
-        <v>6678171</v>
+        <v>6678150</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9399,45 +9390,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901597</v>
+        <v>129901658</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457892</v>
+        <v>457862</v>
       </c>
       <c r="R78" t="n">
-        <v>6678150</v>
+        <v>6678208</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,7 +9506,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R79" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129896383</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -9648,13 +9648,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>458001</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6677916</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,12 +9693,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9725,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9736,42 +9731,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R81" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9790,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9800,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9842,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129903802</v>
+        <v>129896652</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,34 +7669,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457983</v>
+        <v>457954</v>
       </c>
       <c r="R62" t="n">
-        <v>6678105</v>
+        <v>6678018</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7728,7 +7733,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7743,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,7 +7775,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129903740</v>
+        <v>129903802</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -7800,10 +7810,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457907</v>
+        <v>457983</v>
       </c>
       <c r="R63" t="n">
-        <v>6678176</v>
+        <v>6678105</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7835,7 +7845,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7845,7 +7855,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7872,7 +7882,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129906347</v>
+        <v>129903740</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7903,14 +7913,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457859</v>
+        <v>457907</v>
       </c>
       <c r="R64" t="n">
-        <v>6678305</v>
+        <v>6678176</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7942,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7952,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7979,7 +7989,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129895673</v>
+        <v>129906347</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -8010,17 +8020,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457806</v>
+        <v>457859</v>
       </c>
       <c r="R65" t="n">
-        <v>6678097</v>
+        <v>6678305</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8049,7 +8059,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8059,7 +8069,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8086,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129896652</v>
+        <v>129895673</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8097,42 +8107,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457954</v>
+        <v>457806</v>
       </c>
       <c r="R66" t="n">
-        <v>6678018</v>
+        <v>6678097</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8161,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8171,12 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129906213</v>
+        <v>129896799</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457973</v>
+        <v>457943</v>
       </c>
       <c r="R16" t="n">
-        <v>6678187</v>
+        <v>6678103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2589,7 +2589,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2619,7 +2624,7 @@
         <v>129903410</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2723,10 +2728,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129896799</v>
+        <v>129895884</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2734,34 +2739,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457943</v>
+        <v>457831</v>
       </c>
       <c r="R18" t="n">
-        <v>6678103</v>
+        <v>6677903</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2793,7 +2803,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2803,12 +2813,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,10 +2845,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129895884</v>
+        <v>129895608</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2875,13 +2885,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457831</v>
+        <v>457684</v>
       </c>
       <c r="R19" t="n">
-        <v>6677903</v>
+        <v>6678274</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2910,7 +2920,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2920,12 +2930,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,10 +2962,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129895608</v>
+        <v>129906213</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2963,42 +2973,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457684</v>
+        <v>457973</v>
       </c>
       <c r="R20" t="n">
-        <v>6678274</v>
+        <v>6678187</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3072,7 +3072,7 @@
         <v>129903311</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>129906122</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129903889</v>
+        <v>129896363</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,34 +3309,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458004</v>
+        <v>458038</v>
       </c>
       <c r="R23" t="n">
-        <v>6678076</v>
+        <v>6677894</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3368,7 +3373,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3378,7 +3383,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,42 +3410,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129901093</v>
+        <v>129896298</v>
       </c>
       <c r="B24" t="n">
-        <v>92881</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3449,13 +3450,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457936</v>
+        <v>458013</v>
       </c>
       <c r="R24" t="n">
-        <v>6678130</v>
+        <v>6677834</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3484,7 +3485,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,7 +3495,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,38 +3527,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129896298</v>
+        <v>129901093</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>92884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3561,13 +3571,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458013</v>
+        <v>457936</v>
       </c>
       <c r="R25" t="n">
-        <v>6677834</v>
+        <v>6678130</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3596,7 +3606,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,12 +3616,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3638,10 +3643,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129896363</v>
+        <v>129903889</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3649,39 +3654,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458038</v>
+        <v>458004</v>
       </c>
       <c r="R26" t="n">
-        <v>6677894</v>
+        <v>6678076</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3753,7 +3753,7 @@
         <v>129903137</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>129905534</v>
       </c>
       <c r="B28" t="n">
-        <v>81066</v>
+        <v>81069</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,48 +3969,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129906012</v>
+        <v>129895637</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458056</v>
+        <v>457691</v>
       </c>
       <c r="R29" t="n">
-        <v>6678145</v>
+        <v>6678174</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,10 +4076,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903332</v>
+        <v>129904258</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4107,14 +4107,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457738</v>
+        <v>458060</v>
       </c>
       <c r="R30" t="n">
-        <v>6678344</v>
+        <v>6677965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129904258</v>
+        <v>129906012</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4214,14 +4214,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458060</v>
+        <v>458056</v>
       </c>
       <c r="R31" t="n">
-        <v>6677965</v>
+        <v>6678145</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,48 +4290,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129895637</v>
+        <v>129903332</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457691</v>
+        <v>457738</v>
       </c>
       <c r="R32" t="n">
-        <v>6678174</v>
+        <v>6678344</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129901643</v>
+        <v>129895788</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457875</v>
+        <v>457819</v>
       </c>
       <c r="R34" t="n">
-        <v>6678186</v>
+        <v>6677981</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R35" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>129905898</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129903495</v>
+        <v>129896625</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457854</v>
+        <v>457943</v>
       </c>
       <c r="R37" t="n">
-        <v>6678241</v>
+        <v>6678019</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129896625</v>
+        <v>129903495</v>
       </c>
       <c r="B38" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457943</v>
+        <v>457854</v>
       </c>
       <c r="R38" t="n">
-        <v>6678019</v>
+        <v>6678241</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,34 +5070,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5129,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5139,7 +5144,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,10 +5176,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,39 +5187,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R40" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5241,7 +5246,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5251,12 +5256,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5286,7 +5286,7 @@
         <v>129896531</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129905906</v>
+        <v>129895810</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5547,14 +5547,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458187</v>
+        <v>457876</v>
       </c>
       <c r="R43" t="n">
-        <v>6678088</v>
+        <v>6677971</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5596,12 +5596,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 draperade tallar.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,10 +5623,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129895810</v>
+        <v>129905906</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5659,14 +5654,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457876</v>
+        <v>458187</v>
       </c>
       <c r="R44" t="n">
-        <v>6677971</v>
+        <v>6678088</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5698,7 +5693,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5708,7 +5703,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129903770</v>
+        <v>129895784</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,34 +5746,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R45" t="n">
-        <v>6678120</v>
+        <v>6677984</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5815,7 +5820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5842,10 +5852,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129903632</v>
+        <v>129896481</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5873,19 +5883,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R46" t="n">
-        <v>6678255</v>
+        <v>6677968</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5917,7 +5927,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5927,12 +5937,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,10 +5969,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5995,14 +6005,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R47" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6044,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6054,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,10 +6086,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129896481</v>
+        <v>129903770</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6087,29 +6097,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6119,7 +6124,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6677968</v>
+        <v>6678120</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6156,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6166,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6196,7 +6196,7 @@
         <v>129901694</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>129895622</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>129906281</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>129904248</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6758,45 +6758,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129896461</v>
+        <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>92920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457943</v>
+        <v>457867</v>
       </c>
       <c r="R54" t="n">
-        <v>6677964</v>
+        <v>6677937</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6828,7 +6837,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6838,7 +6847,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6865,54 +6879,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129895861</v>
+        <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>92917</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457867</v>
+        <v>457943</v>
       </c>
       <c r="R55" t="n">
-        <v>6677937</v>
+        <v>6677964</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6944,7 +6949,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6954,12 +6959,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129903904</v>
+        <v>129895750</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458009</v>
+        <v>457776</v>
       </c>
       <c r="R56" t="n">
-        <v>6678073</v>
+        <v>6677988</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7106,7 +7106,7 @@
         <v>129905893</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129895750</v>
+        <v>129903904</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457776</v>
+        <v>458009</v>
       </c>
       <c r="R58" t="n">
-        <v>6677988</v>
+        <v>6678073</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129901759</v>
+        <v>129896775</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457813</v>
+        <v>457962</v>
       </c>
       <c r="R59" t="n">
-        <v>6678274</v>
+        <v>6678074</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129896775</v>
+        <v>129904077</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,34 +7445,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457962</v>
+        <v>458047</v>
       </c>
       <c r="R60" t="n">
-        <v>6678074</v>
+        <v>6677984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7504,7 +7509,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7514,7 +7519,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7541,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,39 +7562,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R61" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7616,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7626,12 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7661,7 +7661,7 @@
         <v>129896652</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129903802</v>
+        <v>129895673</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7810,13 +7810,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457983</v>
+        <v>457806</v>
       </c>
       <c r="R63" t="n">
-        <v>6678105</v>
+        <v>6678097</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,10 +7882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903740</v>
+        <v>129903802</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457907</v>
+        <v>457983</v>
       </c>
       <c r="R64" t="n">
-        <v>6678176</v>
+        <v>6678105</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,10 +7989,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129906347</v>
+        <v>129903740</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8020,14 +8020,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457859</v>
+        <v>457907</v>
       </c>
       <c r="R65" t="n">
-        <v>6678305</v>
+        <v>6678176</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129895673</v>
+        <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8127,17 +8127,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457806</v>
+        <v>457859</v>
       </c>
       <c r="R66" t="n">
-        <v>6678097</v>
+        <v>6678305</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,32 +8203,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895677</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>91566</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457806</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678096</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>91563</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8420,7 +8420,7 @@
         <v>129895578</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129901758</v>
+        <v>129896565</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R70" t="n">
-        <v>6678274</v>
+        <v>6678006</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8644,7 +8644,7 @@
         <v>129904132</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8748,10 +8748,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129896565</v>
+        <v>129901758</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457928</v>
+        <v>457814</v>
       </c>
       <c r="R72" t="n">
-        <v>6678006</v>
+        <v>6678274</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129900516</v>
+        <v>129895801</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457915</v>
+        <v>457826</v>
       </c>
       <c r="R73" t="n">
-        <v>6678101</v>
+        <v>6678001</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129901768</v>
+        <v>129900516</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457765</v>
+        <v>457915</v>
       </c>
       <c r="R74" t="n">
-        <v>6678299</v>
+        <v>6678101</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129895801</v>
+        <v>129901768</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457826</v>
+        <v>457765</v>
       </c>
       <c r="R75" t="n">
-        <v>6678001</v>
+        <v>6678299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,45 +9176,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129906105</v>
+        <v>129901658</v>
       </c>
       <c r="B76" t="n">
-        <v>88998</v>
+        <v>92884</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458040</v>
+        <v>457862</v>
       </c>
       <c r="R76" t="n">
-        <v>6678171</v>
+        <v>6678208</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +9255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,7 +9265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9283,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129901597</v>
+        <v>129906105</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>89001</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9294,34 +9303,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457892</v>
+        <v>458040</v>
       </c>
       <c r="R77" t="n">
-        <v>6678150</v>
+        <v>6678171</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9390,54 +9399,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901658</v>
+        <v>129901597</v>
       </c>
       <c r="B78" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457862</v>
+        <v>457892</v>
       </c>
       <c r="R78" t="n">
-        <v>6678208</v>
+        <v>6678150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9517,37 +9517,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R79" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9581,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9591,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9616,7 +9626,7 @@
         <v>129896383</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9723,7 +9733,7 @@
         <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9832,10 +9842,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129895634</v>
+        <v>129903924</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9843,42 +9853,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457704</v>
+        <v>458007</v>
       </c>
       <c r="R82" t="n">
-        <v>6678154</v>
+        <v>6678050</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9912,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2621,7 +2621,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129903410</v>
+        <v>129906213</v>
       </c>
       <c r="B17" t="n">
         <v>79084</v>
@@ -2652,14 +2652,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457802</v>
+        <v>457973</v>
       </c>
       <c r="R17" t="n">
-        <v>6678361</v>
+        <v>6678187</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129895884</v>
+        <v>129903410</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2739,39 +2739,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457831</v>
+        <v>457802</v>
       </c>
       <c r="R18" t="n">
-        <v>6677903</v>
+        <v>6678361</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2803,7 +2798,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2813,12 +2808,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2845,7 +2835,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129895608</v>
+        <v>129895884</v>
       </c>
       <c r="B19" t="n">
         <v>57737</v>
@@ -2885,13 +2875,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457684</v>
+        <v>457831</v>
       </c>
       <c r="R19" t="n">
-        <v>6678274</v>
+        <v>6677903</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,7 +2910,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,12 +2920,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,10 +2952,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129906213</v>
+        <v>129895608</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,37 +2963,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457973</v>
+        <v>457684</v>
       </c>
       <c r="R20" t="n">
-        <v>6678187</v>
+        <v>6678274</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129903311</v>
+        <v>129896298</v>
       </c>
       <c r="B21" t="n">
         <v>57737</v>
@@ -3100,22 +3100,22 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457721</v>
+        <v>458013</v>
       </c>
       <c r="R21" t="n">
-        <v>6678336</v>
+        <v>6677834</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129906122</v>
+        <v>129903311</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,34 +3197,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458021</v>
+        <v>457721</v>
       </c>
       <c r="R22" t="n">
-        <v>6678149</v>
+        <v>6678336</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3256,7 +3261,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3266,12 +3271,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3410,38 +3415,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129896298</v>
+        <v>129901093</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>92884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3450,13 +3459,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458013</v>
+        <v>457936</v>
       </c>
       <c r="R24" t="n">
-        <v>6677834</v>
+        <v>6678130</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3485,7 +3494,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3495,12 +3504,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3527,54 +3531,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129901093</v>
+        <v>129906122</v>
       </c>
       <c r="B25" t="n">
-        <v>92884</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457936</v>
+        <v>458021</v>
       </c>
       <c r="R25" t="n">
-        <v>6678130</v>
+        <v>6678149</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3606,7 +3601,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3616,7 +3611,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129903137</v>
+        <v>129905534</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>81069</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,34 +3761,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457711</v>
+        <v>458192</v>
       </c>
       <c r="R27" t="n">
-        <v>6678336</v>
+        <v>6678014</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,12 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129905534</v>
+        <v>129895637</v>
       </c>
       <c r="B28" t="n">
-        <v>81069</v>
+        <v>91566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458192</v>
+        <v>457691</v>
       </c>
       <c r="R28" t="n">
-        <v>6678014</v>
+        <v>6678174</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3932,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3942,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,48 +3964,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129895637</v>
+        <v>129903137</v>
       </c>
       <c r="B29" t="n">
-        <v>91566</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457691</v>
+        <v>457711</v>
       </c>
       <c r="R29" t="n">
-        <v>6678174</v>
+        <v>6678336</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4039,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4049,7 +4044,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,7 +4076,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129904258</v>
+        <v>129906012</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -4107,14 +4107,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458060</v>
+        <v>458056</v>
       </c>
       <c r="R30" t="n">
-        <v>6677965</v>
+        <v>6678145</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129906012</v>
+        <v>129903332</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -4214,14 +4214,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458056</v>
+        <v>457738</v>
       </c>
       <c r="R31" t="n">
-        <v>6678145</v>
+        <v>6678344</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,7 +4290,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129903332</v>
+        <v>129904258</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -4321,14 +4321,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457738</v>
+        <v>458060</v>
       </c>
       <c r="R32" t="n">
-        <v>6678344</v>
+        <v>6677965</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4504,7 +4504,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R34" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129901643</v>
+        <v>129896625</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,39 +4632,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457875</v>
+        <v>457943</v>
       </c>
       <c r="R35" t="n">
-        <v>6678186</v>
+        <v>6678019</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4696,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4706,12 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4845,10 +4835,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129896625</v>
+        <v>129903495</v>
       </c>
       <c r="B37" t="n">
-        <v>91602</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,21 +4846,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4880,10 +4870,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457943</v>
+        <v>457854</v>
       </c>
       <c r="R37" t="n">
-        <v>6678019</v>
+        <v>6678241</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4915,7 +4905,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4925,7 +4915,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,10 +4942,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129903495</v>
+        <v>129895788</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4963,37 +4953,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457854</v>
+        <v>457819</v>
       </c>
       <c r="R38" t="n">
-        <v>6678241</v>
+        <v>6677981</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5022,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5032,7 +5027,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5283,38 +5283,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>92884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5323,10 +5327,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R41" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5368,12 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,42 +5399,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B42" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R42" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5479,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,7 +5484,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129895784</v>
+        <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,39 +5746,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457792</v>
+        <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6677984</v>
+        <v>6678120</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5815,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5852,7 +5842,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129896481</v>
+        <v>129903632</v>
       </c>
       <c r="B46" t="n">
         <v>57737</v>
@@ -5883,19 +5873,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457943</v>
+        <v>457937</v>
       </c>
       <c r="R46" t="n">
-        <v>6677968</v>
+        <v>6678255</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5927,7 +5917,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5937,12 +5927,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5969,7 +5959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903632</v>
+        <v>129895784</v>
       </c>
       <c r="B47" t="n">
         <v>57737</v>
@@ -6005,14 +5995,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457937</v>
+        <v>457792</v>
       </c>
       <c r="R47" t="n">
-        <v>6678255</v>
+        <v>6677984</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6044,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6054,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6086,10 +6076,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129903770</v>
+        <v>129896481</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6097,24 +6087,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6124,7 +6119,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6678120</v>
+        <v>6677968</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6156,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6166,7 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7103,10 +7103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129905893</v>
+        <v>129903904</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7114,34 +7114,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458190</v>
+        <v>458009</v>
       </c>
       <c r="R57" t="n">
-        <v>6678079</v>
+        <v>6678073</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7173,7 +7178,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7183,7 +7188,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,10 +7220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129903904</v>
+        <v>129905893</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,39 +7231,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458009</v>
+        <v>458190</v>
       </c>
       <c r="R58" t="n">
-        <v>6678073</v>
+        <v>6678079</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7290,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +7300,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7434,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,39 +7445,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R60" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7509,7 +7504,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7519,12 +7514,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7551,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7562,34 +7552,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R61" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7616,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7626,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129896652</v>
+        <v>129895673</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,42 +7669,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457954</v>
+        <v>457806</v>
       </c>
       <c r="R62" t="n">
-        <v>6678018</v>
+        <v>6678097</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7733,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7743,12 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7775,7 +7765,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129895673</v>
+        <v>129903802</v>
       </c>
       <c r="B63" t="n">
         <v>79084</v>
@@ -7810,13 +7800,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457806</v>
+        <v>457983</v>
       </c>
       <c r="R63" t="n">
-        <v>6678097</v>
+        <v>6678105</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7845,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7855,7 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,7 +7872,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903802</v>
+        <v>129903740</v>
       </c>
       <c r="B64" t="n">
         <v>79084</v>
@@ -7917,10 +7907,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457983</v>
+        <v>457907</v>
       </c>
       <c r="R64" t="n">
-        <v>6678105</v>
+        <v>6678176</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7942,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7952,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,7 +7979,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903740</v>
+        <v>129906347</v>
       </c>
       <c r="B65" t="n">
         <v>79084</v>
@@ -8020,14 +8010,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457907</v>
+        <v>457859</v>
       </c>
       <c r="R65" t="n">
-        <v>6678176</v>
+        <v>6678305</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8059,7 +8049,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8059,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129906347</v>
+        <v>129896652</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,34 +8097,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457859</v>
+        <v>457954</v>
       </c>
       <c r="R66" t="n">
-        <v>6678305</v>
+        <v>6678018</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8171,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,32 +8203,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B67" t="n">
-        <v>91566</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R67" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895677</v>
+        <v>129896274</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>91566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457806</v>
+        <v>458013</v>
       </c>
       <c r="R68" t="n">
-        <v>6678096</v>
+        <v>6677833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129904132</v>
+        <v>129901758</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458061</v>
+        <v>457814</v>
       </c>
       <c r="R71" t="n">
-        <v>6677989</v>
+        <v>6678274</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129901758</v>
+        <v>129904132</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457814</v>
+        <v>458061</v>
       </c>
       <c r="R72" t="n">
-        <v>6678274</v>
+        <v>6677989</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129895801</v>
+        <v>129900516</v>
       </c>
       <c r="B73" t="n">
         <v>79084</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457826</v>
+        <v>457915</v>
       </c>
       <c r="R73" t="n">
-        <v>6678001</v>
+        <v>6678101</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129900516</v>
+        <v>129901768</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457915</v>
+        <v>457765</v>
       </c>
       <c r="R74" t="n">
-        <v>6678101</v>
+        <v>6678299</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129901768</v>
+        <v>129895801</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457765</v>
+        <v>457826</v>
       </c>
       <c r="R75" t="n">
-        <v>6678299</v>
+        <v>6678001</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,54 +9176,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901658</v>
+        <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>92884</v>
+        <v>89001</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457862</v>
+        <v>458040</v>
       </c>
       <c r="R76" t="n">
-        <v>6678208</v>
+        <v>6678171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9255,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9265,7 +9256,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9292,10 +9283,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129906105</v>
+        <v>129901597</v>
       </c>
       <c r="B77" t="n">
-        <v>89001</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9303,34 +9294,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458040</v>
+        <v>457892</v>
       </c>
       <c r="R77" t="n">
-        <v>6678171</v>
+        <v>6678150</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9399,45 +9390,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901597</v>
+        <v>129901658</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>92884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457892</v>
+        <v>457862</v>
       </c>
       <c r="R78" t="n">
-        <v>6678150</v>
+        <v>6678208</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129895634</v>
+        <v>129896383</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9517,39 +9517,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457704</v>
+        <v>458001</v>
       </c>
       <c r="R79" t="n">
-        <v>6678154</v>
+        <v>6677916</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9581,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9591,12 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9623,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896383</v>
+        <v>129896578</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -9658,13 +9648,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458001</v>
+        <v>457933</v>
       </c>
       <c r="R80" t="n">
-        <v>6677916</v>
+        <v>6678030</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9693,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9703,7 +9693,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9730,7 +9725,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129896578</v>
+        <v>129903924</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9765,10 +9760,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457933</v>
+        <v>458007</v>
       </c>
       <c r="R81" t="n">
-        <v>6678030</v>
+        <v>6678050</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9800,7 +9795,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9805,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9842,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896799</v>
+        <v>129895884</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,34 +2520,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457943</v>
+        <v>457831</v>
       </c>
       <c r="R16" t="n">
-        <v>6678103</v>
+        <v>6677903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2579,7 +2584,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2589,12 +2594,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2621,10 +2626,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129906213</v>
+        <v>129895608</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2632,37 +2637,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457973</v>
+        <v>457684</v>
       </c>
       <c r="R17" t="n">
-        <v>6678187</v>
+        <v>6678274</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2691,7 +2701,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2701,7 +2711,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,7 +2743,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129903410</v>
+        <v>129906213</v>
       </c>
       <c r="B18" t="n">
         <v>79084</v>
@@ -2759,14 +2774,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457802</v>
+        <v>457973</v>
       </c>
       <c r="R18" t="n">
-        <v>6678361</v>
+        <v>6678187</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2798,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2808,7 +2823,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129895884</v>
+        <v>129903410</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2846,39 +2861,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457831</v>
+        <v>457802</v>
       </c>
       <c r="R19" t="n">
-        <v>6677903</v>
+        <v>6678361</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2910,7 +2920,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2920,12 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,10 +2957,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129895608</v>
+        <v>129896799</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2963,42 +2968,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457684</v>
+        <v>457943</v>
       </c>
       <c r="R20" t="n">
-        <v>6678274</v>
+        <v>6678103</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896298</v>
+        <v>129896363</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458013</v>
+        <v>458038</v>
       </c>
       <c r="R21" t="n">
-        <v>6677834</v>
+        <v>6677894</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,12 +3154,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3186,7 +3181,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129903311</v>
+        <v>129896298</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -3217,22 +3212,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457721</v>
+        <v>458013</v>
       </c>
       <c r="R22" t="n">
-        <v>6678336</v>
+        <v>6677834</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3261,7 +3256,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3271,12 +3266,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3303,10 +3298,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129896363</v>
+        <v>129906122</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,39 +3309,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458038</v>
+        <v>458021</v>
       </c>
       <c r="R23" t="n">
-        <v>6677894</v>
+        <v>6678149</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3378,7 +3368,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3388,7 +3378,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3415,54 +3410,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129901093</v>
+        <v>129903889</v>
       </c>
       <c r="B24" t="n">
-        <v>92884</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457936</v>
+        <v>458004</v>
       </c>
       <c r="R24" t="n">
-        <v>6678130</v>
+        <v>6678076</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3494,7 +3480,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3504,7 +3490,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3531,45 +3517,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129906122</v>
+        <v>129901093</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>92884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458021</v>
+        <v>457936</v>
       </c>
       <c r="R25" t="n">
-        <v>6678149</v>
+        <v>6678130</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3601,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3611,12 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3643,10 +3633,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129903889</v>
+        <v>129903311</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3654,34 +3644,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458004</v>
+        <v>457721</v>
       </c>
       <c r="R26" t="n">
-        <v>6678076</v>
+        <v>6678336</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3713,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3723,7 +3718,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129905534</v>
+        <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>81069</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458192</v>
+        <v>457691</v>
       </c>
       <c r="R27" t="n">
-        <v>6678014</v>
+        <v>6678174</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129895637</v>
+        <v>129906012</v>
       </c>
       <c r="B28" t="n">
-        <v>91566</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457691</v>
+        <v>458056</v>
       </c>
       <c r="R28" t="n">
-        <v>6678174</v>
+        <v>6678145</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903137</v>
+        <v>129903332</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457711</v>
+        <v>457738</v>
       </c>
       <c r="R29" t="n">
-        <v>6678336</v>
+        <v>6678344</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,12 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129906012</v>
+        <v>129903137</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4087,34 +4082,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458056</v>
+        <v>457711</v>
       </c>
       <c r="R30" t="n">
-        <v>6678145</v>
+        <v>6678336</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4146,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4156,7 +4151,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129903332</v>
+        <v>129905534</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>81069</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4194,34 +4194,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457738</v>
+        <v>458192</v>
       </c>
       <c r="R31" t="n">
-        <v>6678344</v>
+        <v>6678014</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4504,7 +4504,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129901643</v>
+        <v>129895788</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457875</v>
+        <v>457819</v>
       </c>
       <c r="R34" t="n">
-        <v>6678186</v>
+        <v>6677981</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4942,7 +4942,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B38" t="n">
         <v>57737</v>
@@ -4973,7 +4973,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R38" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,39 +5070,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R39" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5134,7 +5129,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,12 +5139,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5187,34 +5177,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R40" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5246,7 +5241,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5256,7 +5251,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129903770</v>
+        <v>129896481</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,24 +5746,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -5773,7 +5778,7 @@
         <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6678120</v>
+        <v>6677968</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5815,7 +5820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5842,10 +5852,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129903632</v>
+        <v>129903770</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5853,39 +5863,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R46" t="n">
-        <v>6678255</v>
+        <v>6678120</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5917,7 +5922,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5927,12 +5932,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,7 +5959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B47" t="n">
         <v>57737</v>
@@ -5995,14 +5995,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R47" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,7 +6076,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129896481</v>
+        <v>129895784</v>
       </c>
       <c r="B48" t="n">
         <v>57737</v>
@@ -6107,7 +6107,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R48" t="n">
-        <v>6677968</v>
+        <v>6677984</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129901694</v>
+        <v>129895622</v>
       </c>
       <c r="B49" t="n">
         <v>57737</v>
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457867</v>
+        <v>457689</v>
       </c>
       <c r="R49" t="n">
-        <v>6678204</v>
+        <v>6678248</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,7 +6310,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129895622</v>
+        <v>129901694</v>
       </c>
       <c r="B50" t="n">
         <v>57737</v>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457689</v>
+        <v>457867</v>
       </c>
       <c r="R50" t="n">
-        <v>6678248</v>
+        <v>6678204</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129906281</v>
+        <v>129904248</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,39 +6438,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457937</v>
+        <v>458070</v>
       </c>
       <c r="R51" t="n">
-        <v>6678260</v>
+        <v>6677915</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,7 +6497,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,12 +6507,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6544,7 +6534,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904248</v>
+        <v>129904261</v>
       </c>
       <c r="B52" t="n">
         <v>78841</v>
@@ -6579,10 +6569,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458070</v>
+        <v>458060</v>
       </c>
       <c r="R52" t="n">
-        <v>6677915</v>
+        <v>6677965</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6614,7 +6604,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6624,7 +6614,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6651,10 +6641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129904261</v>
+        <v>129906281</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6662,34 +6652,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458060</v>
+        <v>457937</v>
       </c>
       <c r="R53" t="n">
-        <v>6677965</v>
+        <v>6678260</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6721,7 +6716,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6731,7 +6726,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7434,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,34 +7445,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R60" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7504,7 +7509,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7514,7 +7519,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7541,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,39 +7562,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R61" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7616,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7626,12 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129895673</v>
+        <v>129896652</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,37 +7669,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457806</v>
+        <v>457954</v>
       </c>
       <c r="R62" t="n">
-        <v>6678097</v>
+        <v>6678018</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7733,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7743,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7872,7 +7882,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903740</v>
+        <v>129906347</v>
       </c>
       <c r="B64" t="n">
         <v>79084</v>
@@ -7903,14 +7913,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457907</v>
+        <v>457859</v>
       </c>
       <c r="R64" t="n">
-        <v>6678176</v>
+        <v>6678305</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7942,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7952,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7979,7 +7989,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129906347</v>
+        <v>129903740</v>
       </c>
       <c r="B65" t="n">
         <v>79084</v>
@@ -8010,14 +8020,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457859</v>
+        <v>457907</v>
       </c>
       <c r="R65" t="n">
-        <v>6678305</v>
+        <v>6678176</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8049,7 +8059,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8059,7 +8069,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8086,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129896652</v>
+        <v>129895673</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8097,42 +8107,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457954</v>
+        <v>457806</v>
       </c>
       <c r="R66" t="n">
-        <v>6678018</v>
+        <v>6678097</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8161,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8171,12 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,32 +8203,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895677</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>91566</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457806</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678096</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>91566</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8534,7 +8534,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129896565</v>
+        <v>129901758</v>
       </c>
       <c r="B70" t="n">
         <v>79084</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457928</v>
+        <v>457814</v>
       </c>
       <c r="R70" t="n">
-        <v>6678006</v>
+        <v>6678274</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129901758</v>
+        <v>129904132</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457814</v>
+        <v>458061</v>
       </c>
       <c r="R71" t="n">
-        <v>6678274</v>
+        <v>6677989</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129904132</v>
+        <v>129896565</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458061</v>
+        <v>457928</v>
       </c>
       <c r="R72" t="n">
-        <v>6677989</v>
+        <v>6678006</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129900516</v>
+        <v>129895801</v>
       </c>
       <c r="B73" t="n">
         <v>79084</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457915</v>
+        <v>457826</v>
       </c>
       <c r="R73" t="n">
-        <v>6678101</v>
+        <v>6678001</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129901768</v>
+        <v>129900516</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457765</v>
+        <v>457915</v>
       </c>
       <c r="R74" t="n">
-        <v>6678299</v>
+        <v>6678101</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129895801</v>
+        <v>129901768</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457826</v>
+        <v>457765</v>
       </c>
       <c r="R75" t="n">
-        <v>6678001</v>
+        <v>6678299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,45 +9176,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129906105</v>
+        <v>129901658</v>
       </c>
       <c r="B76" t="n">
-        <v>89001</v>
+        <v>92884</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458040</v>
+        <v>457862</v>
       </c>
       <c r="R76" t="n">
-        <v>6678171</v>
+        <v>6678208</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +9255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,7 +9265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9283,10 +9292,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129901597</v>
+        <v>129906105</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>89001</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9294,34 +9303,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457892</v>
+        <v>458040</v>
       </c>
       <c r="R77" t="n">
-        <v>6678150</v>
+        <v>6678171</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9390,54 +9399,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901658</v>
+        <v>129901597</v>
       </c>
       <c r="B78" t="n">
-        <v>92884</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457862</v>
+        <v>457892</v>
       </c>
       <c r="R78" t="n">
-        <v>6678208</v>
+        <v>6678150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129895634</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,37 +9624,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>457704</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6678154</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,7 +9688,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,12 +9698,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9725,7 +9730,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129903924</v>
+        <v>129896578</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9760,10 +9765,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458007</v>
+        <v>457933</v>
       </c>
       <c r="R81" t="n">
-        <v>6678050</v>
+        <v>6678030</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9795,7 +9800,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9805,7 +9810,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9832,10 +9842,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129895634</v>
+        <v>129903924</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9843,42 +9853,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457704</v>
+        <v>458007</v>
       </c>
       <c r="R82" t="n">
-        <v>6678154</v>
+        <v>6678050</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9912,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2512,7 +2512,7 @@
         <v>129895884</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>129895608</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129906213</v>
+        <v>129903410</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2774,14 +2774,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457973</v>
+        <v>457802</v>
       </c>
       <c r="R18" t="n">
-        <v>6678187</v>
+        <v>6678361</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129903410</v>
+        <v>129896799</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2881,14 +2881,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457802</v>
+        <v>457943</v>
       </c>
       <c r="R19" t="n">
-        <v>6678361</v>
+        <v>6678103</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,7 +2930,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,10 +2962,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896799</v>
+        <v>129906213</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,14 +2993,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457943</v>
+        <v>457973</v>
       </c>
       <c r="R20" t="n">
-        <v>6678103</v>
+        <v>6678187</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896363</v>
+        <v>129906122</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,39 +3080,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458038</v>
+        <v>458021</v>
       </c>
       <c r="R21" t="n">
-        <v>6677894</v>
+        <v>6678149</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,7 +3149,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129896298</v>
+        <v>129903889</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,42 +3192,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458013</v>
+        <v>458004</v>
       </c>
       <c r="R22" t="n">
-        <v>6677834</v>
+        <v>6678076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3266,12 +3261,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3298,10 +3288,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129906122</v>
+        <v>129903311</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,34 +3299,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458021</v>
+        <v>457721</v>
       </c>
       <c r="R23" t="n">
-        <v>6678149</v>
+        <v>6678336</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3368,7 +3363,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3378,12 +3373,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,10 +3405,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129903889</v>
+        <v>129896298</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,37 +3416,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458004</v>
+        <v>458013</v>
       </c>
       <c r="R24" t="n">
-        <v>6678076</v>
+        <v>6677834</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3490,7 +3490,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3517,42 +3522,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129901093</v>
+        <v>129896363</v>
       </c>
       <c r="B25" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3561,10 +3562,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457936</v>
+        <v>458038</v>
       </c>
       <c r="R25" t="n">
-        <v>6678130</v>
+        <v>6677894</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3596,7 +3597,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3607,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,50 +3634,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129903311</v>
+        <v>129901093</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>92887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457721</v>
+        <v>457936</v>
       </c>
       <c r="R26" t="n">
-        <v>6678336</v>
+        <v>6678130</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3708,7 +3713,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3723,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3753,7 +3753,7 @@
         <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129906012</v>
+        <v>129905534</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>81072</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458056</v>
+        <v>458192</v>
       </c>
       <c r="R28" t="n">
-        <v>6678145</v>
+        <v>6678014</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903332</v>
+        <v>129906012</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457738</v>
+        <v>458056</v>
       </c>
       <c r="R29" t="n">
-        <v>6678344</v>
+        <v>6678145</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903137</v>
+        <v>129903332</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4082,21 +4082,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457711</v>
+        <v>457738</v>
       </c>
       <c r="R30" t="n">
-        <v>6678336</v>
+        <v>6678344</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,12 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129905534</v>
+        <v>129903137</v>
       </c>
       <c r="B31" t="n">
-        <v>81069</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4194,34 +4189,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458192</v>
+        <v>457711</v>
       </c>
       <c r="R31" t="n">
-        <v>6678014</v>
+        <v>6678336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4258,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4293,7 +4293,7 @@
         <v>129904258</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129895788</v>
+        <v>129896625</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4515,42 +4515,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457819</v>
+        <v>457943</v>
       </c>
       <c r="R34" t="n">
-        <v>6677981</v>
+        <v>6678019</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,12 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4621,10 +4611,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129896625</v>
+        <v>129895788</v>
       </c>
       <c r="B35" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,37 +4622,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457943</v>
+        <v>457819</v>
       </c>
       <c r="R35" t="n">
-        <v>6678019</v>
+        <v>6677981</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4691,7 +4686,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4696,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4731,7 +4731,7 @@
         <v>129905898</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>129903495</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>129901643</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,34 +5070,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5129,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5139,7 +5144,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,10 +5176,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,39 +5187,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R40" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5241,7 +5246,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5251,12 +5256,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5283,42 +5283,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B41" t="n">
-        <v>92884</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5327,10 +5323,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R41" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5362,7 +5358,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5368,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,38 +5400,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>92887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R42" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,12 +5489,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5519,7 +5519,7 @@
         <v>129895810</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>129905906</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129896481</v>
+        <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,29 +5746,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -5778,7 +5773,7 @@
         <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6677968</v>
+        <v>6678120</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5815,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5852,10 +5842,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129903770</v>
+        <v>129895784</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5863,34 +5853,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R46" t="n">
-        <v>6678120</v>
+        <v>6677984</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5922,7 +5917,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5932,7 +5927,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,10 +5959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903632</v>
+        <v>129896481</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,19 +5990,19 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R47" t="n">
-        <v>6678255</v>
+        <v>6677968</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,10 +6076,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R48" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6196,7 +6196,7 @@
         <v>129895622</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>129901694</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129904248</v>
+        <v>129906281</v>
       </c>
       <c r="B51" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,34 +6438,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458070</v>
+        <v>457937</v>
       </c>
       <c r="R51" t="n">
-        <v>6677915</v>
+        <v>6678260</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6507,7 +6512,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,10 +6544,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904261</v>
+        <v>129904248</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,10 +6579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458060</v>
+        <v>458070</v>
       </c>
       <c r="R52" t="n">
-        <v>6677965</v>
+        <v>6677915</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6604,7 +6614,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6614,7 +6624,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6641,10 +6651,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129906281</v>
+        <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6652,39 +6662,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457937</v>
+        <v>458060</v>
       </c>
       <c r="R53" t="n">
-        <v>6678260</v>
+        <v>6677965</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6716,7 +6721,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6726,12 +6731,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6758,54 +6758,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129895861</v>
+        <v>129896461</v>
       </c>
       <c r="B54" t="n">
-        <v>92920</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457867</v>
+        <v>457943</v>
       </c>
       <c r="R54" t="n">
-        <v>6677937</v>
+        <v>6677964</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6837,7 +6828,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6847,12 +6838,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6879,45 +6865,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129896461</v>
+        <v>129895861</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>92923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457943</v>
+        <v>457867</v>
       </c>
       <c r="R55" t="n">
-        <v>6677964</v>
+        <v>6677937</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6949,7 +6944,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6959,7 +6954,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6989,7 +6989,7 @@
         <v>129895750</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7103,10 +7103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129903904</v>
+        <v>129905893</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7114,39 +7114,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458009</v>
+        <v>458190</v>
       </c>
       <c r="R57" t="n">
-        <v>6678073</v>
+        <v>6678079</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7178,7 +7173,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7188,12 +7183,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7220,10 +7210,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129905893</v>
+        <v>129903904</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7231,34 +7221,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458190</v>
+        <v>458009</v>
       </c>
       <c r="R58" t="n">
-        <v>6678079</v>
+        <v>6678073</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7290,7 +7285,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7300,7 +7295,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7330,7 +7330,7 @@
         <v>129896775</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,39 +7445,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R60" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7509,7 +7504,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7519,12 +7514,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7551,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7562,34 +7552,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R61" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7616,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7626,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129896652</v>
+        <v>129895673</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,42 +7669,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457954</v>
+        <v>457806</v>
       </c>
       <c r="R62" t="n">
-        <v>6678018</v>
+        <v>6678097</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7733,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7743,12 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7775,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129903802</v>
+        <v>129896652</v>
       </c>
       <c r="B63" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7786,34 +7776,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457983</v>
+        <v>457954</v>
       </c>
       <c r="R63" t="n">
-        <v>6678105</v>
+        <v>6678018</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7845,7 +7840,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7855,7 +7850,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,10 +7882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129906347</v>
+        <v>129903802</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7913,14 +7913,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457859</v>
+        <v>457983</v>
       </c>
       <c r="R64" t="n">
-        <v>6678305</v>
+        <v>6678105</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7992,7 +7992,7 @@
         <v>129903740</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129895673</v>
+        <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8127,17 +8127,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457806</v>
+        <v>457859</v>
       </c>
       <c r="R66" t="n">
-        <v>6678097</v>
+        <v>6678305</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,45 +8203,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129896274</v>
+        <v>129895578</v>
       </c>
       <c r="B67" t="n">
-        <v>91566</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458013</v>
+        <v>457678</v>
       </c>
       <c r="R67" t="n">
-        <v>6677833</v>
+        <v>6678274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8288,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8313,7 +8323,7 @@
         <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8417,50 +8427,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>91569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R69" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8492,7 +8497,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8502,12 +8507,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129901758</v>
+        <v>129896565</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R70" t="n">
-        <v>6678274</v>
+        <v>6678006</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129904132</v>
+        <v>129901758</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458061</v>
+        <v>457814</v>
       </c>
       <c r="R71" t="n">
-        <v>6677989</v>
+        <v>6678274</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129896565</v>
+        <v>129904132</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457928</v>
+        <v>458061</v>
       </c>
       <c r="R72" t="n">
-        <v>6678006</v>
+        <v>6677989</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129895801</v>
+        <v>129900516</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457826</v>
+        <v>457915</v>
       </c>
       <c r="R73" t="n">
-        <v>6678001</v>
+        <v>6678101</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129900516</v>
+        <v>129901768</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457915</v>
+        <v>457765</v>
       </c>
       <c r="R74" t="n">
-        <v>6678101</v>
+        <v>6678299</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129901768</v>
+        <v>129895801</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457765</v>
+        <v>457826</v>
       </c>
       <c r="R75" t="n">
-        <v>6678299</v>
+        <v>6678001</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,54 +9176,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901658</v>
+        <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>92884</v>
+        <v>89004</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457862</v>
+        <v>458040</v>
       </c>
       <c r="R76" t="n">
-        <v>6678208</v>
+        <v>6678171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9255,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9265,7 +9256,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9292,10 +9283,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129906105</v>
+        <v>129901597</v>
       </c>
       <c r="B77" t="n">
-        <v>89001</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9303,34 +9294,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458040</v>
+        <v>457892</v>
       </c>
       <c r="R77" t="n">
-        <v>6678171</v>
+        <v>6678150</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9399,45 +9390,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901597</v>
+        <v>129901658</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>92887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457892</v>
+        <v>457862</v>
       </c>
       <c r="R78" t="n">
-        <v>6678150</v>
+        <v>6678208</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9509,7 +9509,7 @@
         <v>129896383</v>
       </c>
       <c r="B79" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,42 +9624,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R80" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9688,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9698,12 +9693,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9730,10 +9725,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129896578</v>
+        <v>129895634</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9741,37 +9736,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457933</v>
+        <v>457704</v>
       </c>
       <c r="R81" t="n">
-        <v>6678030</v>
+        <v>6678154</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9845,7 +9845,7 @@
         <v>129903924</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2743,7 +2743,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129903410</v>
+        <v>129906213</v>
       </c>
       <c r="B18" t="n">
         <v>79087</v>
@@ -2774,14 +2774,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457802</v>
+        <v>457973</v>
       </c>
       <c r="R18" t="n">
-        <v>6678361</v>
+        <v>6678187</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2850,7 +2850,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129896799</v>
+        <v>129903410</v>
       </c>
       <c r="B19" t="n">
         <v>79087</v>
@@ -2881,14 +2881,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457943</v>
+        <v>457802</v>
       </c>
       <c r="R19" t="n">
-        <v>6678103</v>
+        <v>6678361</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,12 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,7 +2957,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129906213</v>
+        <v>129896799</v>
       </c>
       <c r="B20" t="n">
         <v>79087</v>
@@ -2993,14 +2988,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457973</v>
+        <v>457943</v>
       </c>
       <c r="R20" t="n">
-        <v>6678187</v>
+        <v>6678103</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129895637</v>
+        <v>129905534</v>
       </c>
       <c r="B27" t="n">
-        <v>91569</v>
+        <v>81072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457691</v>
+        <v>458192</v>
       </c>
       <c r="R27" t="n">
-        <v>6678174</v>
+        <v>6678014</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129905534</v>
+        <v>129906012</v>
       </c>
       <c r="B28" t="n">
-        <v>81072</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458192</v>
+        <v>458056</v>
       </c>
       <c r="R28" t="n">
-        <v>6678014</v>
+        <v>6678145</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129906012</v>
+        <v>129903332</v>
       </c>
       <c r="B29" t="n">
         <v>79087</v>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458056</v>
+        <v>457738</v>
       </c>
       <c r="R29" t="n">
-        <v>6678145</v>
+        <v>6678344</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4071,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903332</v>
+        <v>129904258</v>
       </c>
       <c r="B30" t="n">
         <v>79087</v>
@@ -4102,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457738</v>
+        <v>458060</v>
       </c>
       <c r="R30" t="n">
-        <v>6678344</v>
+        <v>6677965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4290,32 +4290,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129904258</v>
+        <v>129895637</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458060</v>
+        <v>457691</v>
       </c>
       <c r="R32" t="n">
-        <v>6677965</v>
+        <v>6678174</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5283,38 +5283,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>92887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5323,10 +5327,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R41" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5368,12 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,42 +5399,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B42" t="n">
-        <v>92887</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R42" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5479,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,7 +5484,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7434,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,34 +7445,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R60" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7504,7 +7509,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7514,7 +7519,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7541,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,39 +7562,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R61" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7616,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7626,12 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129905534</v>
+        <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>81072</v>
+        <v>91569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458192</v>
+        <v>457691</v>
       </c>
       <c r="R27" t="n">
-        <v>6678014</v>
+        <v>6678174</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129906012</v>
+        <v>129905534</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>81072</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458056</v>
+        <v>458192</v>
       </c>
       <c r="R28" t="n">
-        <v>6678145</v>
+        <v>6678014</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903332</v>
+        <v>129906012</v>
       </c>
       <c r="B29" t="n">
         <v>79087</v>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457738</v>
+        <v>458056</v>
       </c>
       <c r="R29" t="n">
-        <v>6678344</v>
+        <v>6678145</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4071,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129904258</v>
+        <v>129903332</v>
       </c>
       <c r="B30" t="n">
         <v>79087</v>
@@ -4102,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458060</v>
+        <v>457738</v>
       </c>
       <c r="R30" t="n">
-        <v>6677965</v>
+        <v>6678344</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4290,32 +4290,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129895637</v>
+        <v>129904258</v>
       </c>
       <c r="B32" t="n">
-        <v>91569</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457691</v>
+        <v>458060</v>
       </c>
       <c r="R32" t="n">
-        <v>6678174</v>
+        <v>6677965</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -8203,10 +8203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129895677</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8214,39 +8214,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>457806</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6678096</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,12 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8320,10 +8310,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895677</v>
+        <v>129895578</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8331,34 +8321,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457806</v>
+        <v>457678</v>
       </c>
       <c r="R68" t="n">
-        <v>6678096</v>
+        <v>6678274</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8385,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8395,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9506,7 +9506,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B79" t="n">
         <v>79087</v>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R79" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129896383</v>
       </c>
       <c r="B80" t="n">
         <v>79087</v>
@@ -9648,13 +9648,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>458001</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6677916</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,12 +9693,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9725,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9736,42 +9731,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R81" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9790,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9800,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9842,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129895884</v>
+        <v>129896799</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,39 +2520,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457831</v>
+        <v>457943</v>
       </c>
       <c r="R16" t="n">
-        <v>6677903</v>
+        <v>6678103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2584,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2594,12 +2589,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2626,7 +2621,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129895608</v>
+        <v>129895884</v>
       </c>
       <c r="B17" t="n">
         <v>57740</v>
@@ -2666,13 +2661,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457684</v>
+        <v>457831</v>
       </c>
       <c r="R17" t="n">
-        <v>6678274</v>
+        <v>6677903</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2711,12 +2706,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129906213</v>
+        <v>129895608</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2754,37 +2749,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457973</v>
+        <v>457684</v>
       </c>
       <c r="R18" t="n">
-        <v>6678187</v>
+        <v>6678274</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,7 +2823,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2850,10 +2855,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129903410</v>
+        <v>129906213</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2881,14 +2886,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457802</v>
+        <v>457973</v>
       </c>
       <c r="R19" t="n">
-        <v>6678361</v>
+        <v>6678187</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2920,7 +2925,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,7 +2935,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,10 +2962,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896799</v>
+        <v>129903410</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,14 +2993,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457943</v>
+        <v>457802</v>
       </c>
       <c r="R20" t="n">
-        <v>6678103</v>
+        <v>6678361</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129906122</v>
+        <v>129896298</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,37 +3080,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458021</v>
+        <v>458013</v>
       </c>
       <c r="R21" t="n">
-        <v>6678149</v>
+        <v>6677834</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,12 +3154,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,10 +3186,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129903889</v>
+        <v>129896363</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,34 +3197,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458004</v>
+        <v>458038</v>
       </c>
       <c r="R22" t="n">
-        <v>6678076</v>
+        <v>6677894</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3251,7 +3261,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3261,7 +3271,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3288,50 +3298,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129903311</v>
+        <v>129901093</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>92888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457721</v>
+        <v>457936</v>
       </c>
       <c r="R23" t="n">
-        <v>6678336</v>
+        <v>6678130</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3363,7 +3377,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3373,12 +3387,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,10 +3414,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129896298</v>
+        <v>129906122</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3416,42 +3425,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458013</v>
+        <v>458021</v>
       </c>
       <c r="R24" t="n">
-        <v>6677834</v>
+        <v>6678149</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3480,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3490,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Barkfläk gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3522,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129896363</v>
+        <v>129903889</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3533,39 +3537,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458038</v>
+        <v>458004</v>
       </c>
       <c r="R25" t="n">
-        <v>6677894</v>
+        <v>6678076</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3597,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3607,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3634,54 +3633,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129901093</v>
+        <v>129903311</v>
       </c>
       <c r="B26" t="n">
-        <v>92887</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457936</v>
+        <v>457721</v>
       </c>
       <c r="R26" t="n">
-        <v>6678130</v>
+        <v>6678336</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3713,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3723,7 +3718,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129895637</v>
+        <v>129905534</v>
       </c>
       <c r="B27" t="n">
-        <v>91569</v>
+        <v>81073</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457691</v>
+        <v>458192</v>
       </c>
       <c r="R27" t="n">
-        <v>6678174</v>
+        <v>6678014</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129905534</v>
+        <v>129906012</v>
       </c>
       <c r="B28" t="n">
-        <v>81072</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458192</v>
+        <v>458056</v>
       </c>
       <c r="R28" t="n">
-        <v>6678014</v>
+        <v>6678145</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129906012</v>
+        <v>129903332</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458056</v>
+        <v>457738</v>
       </c>
       <c r="R29" t="n">
-        <v>6678145</v>
+        <v>6678344</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903332</v>
+        <v>129904258</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4102,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457738</v>
+        <v>458060</v>
       </c>
       <c r="R30" t="n">
-        <v>6678344</v>
+        <v>6677965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,48 +4178,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129903137</v>
+        <v>129895637</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457711</v>
+        <v>457691</v>
       </c>
       <c r="R31" t="n">
-        <v>6678336</v>
+        <v>6678174</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,12 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,10 +4285,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129904258</v>
+        <v>129903137</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,34 +4296,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458060</v>
+        <v>457711</v>
       </c>
       <c r="R32" t="n">
-        <v>6677965</v>
+        <v>6678336</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4360,7 +4355,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4365,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129896625</v>
+        <v>129905898</v>
       </c>
       <c r="B34" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457943</v>
+        <v>458188</v>
       </c>
       <c r="R34" t="n">
-        <v>6678019</v>
+        <v>6678089</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4611,10 +4611,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129895788</v>
+        <v>129903495</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4622,42 +4622,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457819</v>
+        <v>457854</v>
       </c>
       <c r="R35" t="n">
-        <v>6677981</v>
+        <v>6678241</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4686,7 +4681,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4696,12 +4691,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,10 +4718,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129905898</v>
+        <v>129896625</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,34 +4729,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458188</v>
+        <v>457943</v>
       </c>
       <c r="R36" t="n">
-        <v>6678089</v>
+        <v>6678019</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4798,7 +4788,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4808,7 +4798,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,10 +4825,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129903495</v>
+        <v>129895788</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,37 +4836,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457854</v>
+        <v>457819</v>
       </c>
       <c r="R37" t="n">
-        <v>6678241</v>
+        <v>6677981</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4905,7 +4900,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4915,7 +4910,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,39 +5070,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R39" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5134,7 +5129,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,12 +5139,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5187,34 +5177,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R40" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5246,7 +5241,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5256,7 +5251,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5283,42 +5283,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B41" t="n">
-        <v>92887</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5327,10 +5323,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R41" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5362,7 +5358,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5368,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,38 +5400,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>92888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R42" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,12 +5489,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5519,7 +5519,7 @@
         <v>129895810</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>129905906</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129906281</v>
+        <v>129904248</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,39 +6438,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457937</v>
+        <v>458070</v>
       </c>
       <c r="R51" t="n">
-        <v>6678260</v>
+        <v>6677915</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,7 +6497,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,12 +6507,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6544,10 +6534,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904248</v>
+        <v>129904261</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6579,10 +6569,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458070</v>
+        <v>458060</v>
       </c>
       <c r="R52" t="n">
-        <v>6677915</v>
+        <v>6677965</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6614,7 +6604,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6624,7 +6614,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6651,10 +6641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129904261</v>
+        <v>129906281</v>
       </c>
       <c r="B53" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6662,34 +6652,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458060</v>
+        <v>457937</v>
       </c>
       <c r="R53" t="n">
-        <v>6677965</v>
+        <v>6678260</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6721,7 +6716,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6731,7 +6726,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6758,45 +6758,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129896461</v>
+        <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>92924</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457943</v>
+        <v>457867</v>
       </c>
       <c r="R54" t="n">
-        <v>6677964</v>
+        <v>6677937</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6828,7 +6837,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6838,7 +6847,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6865,54 +6879,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129895861</v>
+        <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>92923</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457867</v>
+        <v>457943</v>
       </c>
       <c r="R55" t="n">
-        <v>6677937</v>
+        <v>6677964</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6944,7 +6949,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6954,12 +6959,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129895750</v>
+        <v>129905893</v>
       </c>
       <c r="B56" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,39 +6997,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457776</v>
+        <v>458190</v>
       </c>
       <c r="R56" t="n">
-        <v>6677988</v>
+        <v>6678079</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7061,7 +7056,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7071,12 +7066,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7103,10 +7093,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129905893</v>
+        <v>129895750</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7114,34 +7104,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458190</v>
+        <v>457776</v>
       </c>
       <c r="R57" t="n">
-        <v>6678079</v>
+        <v>6677988</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7173,7 +7168,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7183,7 +7178,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129896775</v>
+        <v>129904077</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,34 +7338,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457962</v>
+        <v>458047</v>
       </c>
       <c r="R59" t="n">
-        <v>6678074</v>
+        <v>6677984</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7402,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7412,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,10 +7444,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129904077</v>
+        <v>129896775</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,39 +7455,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458047</v>
+        <v>457962</v>
       </c>
       <c r="R60" t="n">
-        <v>6677984</v>
+        <v>6678074</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7509,7 +7514,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7519,12 +7524,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7554,7 +7554,7 @@
         <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>129895673</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>129903802</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>129903740</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895677</v>
+        <v>129895578</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8214,34 +8214,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457806</v>
+        <v>457678</v>
       </c>
       <c r="R67" t="n">
-        <v>6678096</v>
+        <v>6678274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8288,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,50 +8320,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>91570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R68" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8385,7 +8390,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8395,12 +8400,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,32 +8427,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B69" t="n">
-        <v>91569</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R69" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8537,7 +8537,7 @@
         <v>129896565</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>129901758</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>129904132</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>129900516</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>129901768</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>129895801</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9283,45 +9283,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129901597</v>
+        <v>129901658</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>92888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457892</v>
+        <v>457862</v>
       </c>
       <c r="R77" t="n">
-        <v>6678150</v>
+        <v>6678208</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9390,54 +9399,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901658</v>
+        <v>129901597</v>
       </c>
       <c r="B78" t="n">
-        <v>92887</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457862</v>
+        <v>457892</v>
       </c>
       <c r="R78" t="n">
-        <v>6678208</v>
+        <v>6678150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9509,7 +9509,7 @@
         <v>129903924</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896383</v>
+        <v>129895634</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,34 +9624,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458001</v>
+        <v>457704</v>
       </c>
       <c r="R80" t="n">
-        <v>6677916</v>
+        <v>6678154</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9683,7 +9688,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,7 +9698,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9720,10 +9730,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129896578</v>
+        <v>129896383</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9755,13 +9765,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457933</v>
+        <v>458001</v>
       </c>
       <c r="R81" t="n">
-        <v>6678030</v>
+        <v>6677916</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9790,7 +9800,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9800,12 +9810,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9832,10 +9837,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B82" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9843,42 +9848,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R82" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -5842,7 +5842,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B46" t="n">
         <v>57740</v>
@@ -5878,14 +5878,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R46" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,7 +5959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129896481</v>
+        <v>129895784</v>
       </c>
       <c r="B47" t="n">
         <v>57740</v>
@@ -5990,7 +5990,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R47" t="n">
-        <v>6677968</v>
+        <v>6677984</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,7 +6076,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129903632</v>
+        <v>129896481</v>
       </c>
       <c r="B48" t="n">
         <v>57740</v>
@@ -6107,19 +6107,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6678255</v>
+        <v>6677968</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6758,54 +6758,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129895861</v>
+        <v>129896461</v>
       </c>
       <c r="B54" t="n">
-        <v>92924</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457867</v>
+        <v>457943</v>
       </c>
       <c r="R54" t="n">
-        <v>6677937</v>
+        <v>6677964</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6837,7 +6828,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6847,12 +6838,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6879,45 +6865,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129896461</v>
+        <v>129895861</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>92924</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457943</v>
+        <v>457867</v>
       </c>
       <c r="R55" t="n">
-        <v>6677964</v>
+        <v>6677937</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6949,7 +6944,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6959,7 +6954,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7658,7 +7658,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129895673</v>
+        <v>129903802</v>
       </c>
       <c r="B62" t="n">
         <v>79088</v>
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457806</v>
+        <v>457983</v>
       </c>
       <c r="R62" t="n">
-        <v>6678097</v>
+        <v>6678105</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129896652</v>
+        <v>129903740</v>
       </c>
       <c r="B63" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7776,39 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457954</v>
+        <v>457907</v>
       </c>
       <c r="R63" t="n">
-        <v>6678018</v>
+        <v>6678176</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7840,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7850,12 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,7 +7872,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903802</v>
+        <v>129906347</v>
       </c>
       <c r="B64" t="n">
         <v>79088</v>
@@ -7913,14 +7903,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457983</v>
+        <v>457859</v>
       </c>
       <c r="R64" t="n">
-        <v>6678105</v>
+        <v>6678305</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7942,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7952,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,7 +7979,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903740</v>
+        <v>129895673</v>
       </c>
       <c r="B65" t="n">
         <v>79088</v>
@@ -8024,13 +8014,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457907</v>
+        <v>457806</v>
       </c>
       <c r="R65" t="n">
-        <v>6678176</v>
+        <v>6678097</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,7 +8049,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8059,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129906347</v>
+        <v>129896652</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,34 +8097,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457859</v>
+        <v>457954</v>
       </c>
       <c r="R66" t="n">
-        <v>6678305</v>
+        <v>6678018</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8171,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,50 +8203,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>91570</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,12 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8320,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>91570</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8355,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,10 +8417,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895677</v>
+        <v>129895578</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8438,34 +8428,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457806</v>
+        <v>457678</v>
       </c>
       <c r="R69" t="n">
-        <v>6678096</v>
+        <v>6678274</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8497,7 +8492,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,7 +8502,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9506,7 +9506,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129903924</v>
+        <v>129896383</v>
       </c>
       <c r="B79" t="n">
         <v>79088</v>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458007</v>
+        <v>458001</v>
       </c>
       <c r="R79" t="n">
-        <v>6678050</v>
+        <v>6677916</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B80" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,42 +9624,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R80" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9688,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9698,12 +9693,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9730,7 +9725,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B81" t="n">
         <v>79088</v>
@@ -9765,13 +9760,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R81" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9795,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,7 +9805,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9837,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129896578</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9848,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457933</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678030</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -3069,38 +3069,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896298</v>
+        <v>129901093</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>92888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3109,13 +3113,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458013</v>
+        <v>457936</v>
       </c>
       <c r="R21" t="n">
-        <v>6677834</v>
+        <v>6678130</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3148,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,12 +3158,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3298,42 +3297,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129901093</v>
+        <v>129896298</v>
       </c>
       <c r="B23" t="n">
-        <v>92888</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3342,13 +3337,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457936</v>
+        <v>458013</v>
       </c>
       <c r="R23" t="n">
-        <v>6678130</v>
+        <v>6677834</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3377,7 +3372,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3387,7 +3382,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129905534</v>
+        <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>81073</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458192</v>
+        <v>457691</v>
       </c>
       <c r="R27" t="n">
-        <v>6678014</v>
+        <v>6678174</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129906012</v>
+        <v>129905534</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>81073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458056</v>
+        <v>458192</v>
       </c>
       <c r="R28" t="n">
-        <v>6678145</v>
+        <v>6678014</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903332</v>
+        <v>129906012</v>
       </c>
       <c r="B29" t="n">
         <v>79088</v>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457738</v>
+        <v>458056</v>
       </c>
       <c r="R29" t="n">
-        <v>6678344</v>
+        <v>6678145</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4071,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129904258</v>
+        <v>129903332</v>
       </c>
       <c r="B30" t="n">
         <v>79088</v>
@@ -4102,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458060</v>
+        <v>457738</v>
       </c>
       <c r="R30" t="n">
-        <v>6677965</v>
+        <v>6678344</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,32 +4178,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129895637</v>
+        <v>129904258</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457691</v>
+        <v>458060</v>
       </c>
       <c r="R31" t="n">
-        <v>6678174</v>
+        <v>6677965</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129905898</v>
+        <v>129896625</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458188</v>
+        <v>457943</v>
       </c>
       <c r="R34" t="n">
-        <v>6678089</v>
+        <v>6678019</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4611,10 +4611,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129903495</v>
+        <v>129895788</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4622,37 +4622,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457854</v>
+        <v>457819</v>
       </c>
       <c r="R35" t="n">
-        <v>6678241</v>
+        <v>6677981</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4681,7 +4686,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4691,7 +4696,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4718,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129896625</v>
+        <v>129905898</v>
       </c>
       <c r="B36" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4729,34 +4739,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457943</v>
+        <v>458188</v>
       </c>
       <c r="R36" t="n">
-        <v>6678019</v>
+        <v>6678089</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4788,7 +4798,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4798,7 +4808,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4825,10 +4835,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129895788</v>
+        <v>129903495</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,42 +4846,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457819</v>
+        <v>457854</v>
       </c>
       <c r="R37" t="n">
-        <v>6677981</v>
+        <v>6678241</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4900,7 +4905,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4910,12 +4915,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,34 +5070,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5129,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5139,7 +5144,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,10 +5176,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,39 +5187,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R40" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5241,7 +5246,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5251,12 +5256,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6758,45 +6758,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129896461</v>
+        <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>92924</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457943</v>
+        <v>457867</v>
       </c>
       <c r="R54" t="n">
-        <v>6677964</v>
+        <v>6677937</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6828,7 +6837,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6838,7 +6847,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6865,54 +6879,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129895861</v>
+        <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>92924</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457867</v>
+        <v>457943</v>
       </c>
       <c r="R55" t="n">
-        <v>6677937</v>
+        <v>6677964</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6944,7 +6949,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6954,12 +6959,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7658,7 +7658,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129903802</v>
+        <v>129895673</v>
       </c>
       <c r="B62" t="n">
         <v>79088</v>
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457983</v>
+        <v>457806</v>
       </c>
       <c r="R62" t="n">
-        <v>6678105</v>
+        <v>6678097</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129903740</v>
+        <v>129896652</v>
       </c>
       <c r="B63" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7776,34 +7776,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457907</v>
+        <v>457954</v>
       </c>
       <c r="R63" t="n">
-        <v>6678176</v>
+        <v>6678018</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7835,7 +7840,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7845,7 +7850,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7872,7 +7882,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129906347</v>
+        <v>129903802</v>
       </c>
       <c r="B64" t="n">
         <v>79088</v>
@@ -7903,14 +7913,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457859</v>
+        <v>457983</v>
       </c>
       <c r="R64" t="n">
-        <v>6678305</v>
+        <v>6678105</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7942,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7952,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7979,7 +7989,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129895673</v>
+        <v>129903740</v>
       </c>
       <c r="B65" t="n">
         <v>79088</v>
@@ -8014,13 +8024,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457806</v>
+        <v>457907</v>
       </c>
       <c r="R65" t="n">
-        <v>6678097</v>
+        <v>6678176</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8049,7 +8059,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8059,7 +8069,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8086,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129896652</v>
+        <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8097,39 +8107,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457954</v>
+        <v>457859</v>
       </c>
       <c r="R66" t="n">
-        <v>6678018</v>
+        <v>6678305</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8161,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8171,12 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,45 +8203,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129896274</v>
+        <v>129895578</v>
       </c>
       <c r="B67" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458013</v>
+        <v>457678</v>
       </c>
       <c r="R67" t="n">
-        <v>6677833</v>
+        <v>6678274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8288,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,32 +8320,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895677</v>
+        <v>129896274</v>
       </c>
       <c r="B68" t="n">
-        <v>79088</v>
+        <v>91570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8345,10 +8355,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457806</v>
+        <v>458013</v>
       </c>
       <c r="R68" t="n">
-        <v>6678096</v>
+        <v>6677833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8380,7 +8390,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8390,7 +8400,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8417,10 +8427,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895578</v>
+        <v>129895677</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8428,39 +8438,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457678</v>
+        <v>457806</v>
       </c>
       <c r="R69" t="n">
-        <v>6678274</v>
+        <v>6678096</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8492,7 +8497,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8502,12 +8507,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9506,7 +9506,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B79" t="n">
         <v>79088</v>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R79" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129895634</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,37 +9624,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>457704</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6678154</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,7 +9688,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,12 +9698,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9725,7 +9730,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129903924</v>
+        <v>129896383</v>
       </c>
       <c r="B81" t="n">
         <v>79088</v>
@@ -9760,13 +9765,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458007</v>
+        <v>458001</v>
       </c>
       <c r="R81" t="n">
-        <v>6678050</v>
+        <v>6677916</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9795,7 +9800,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9805,7 +9810,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9832,10 +9837,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B82" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9843,42 +9848,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R82" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2512,7 +2512,7 @@
         <v>129896799</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129906213</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129903410</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3069,54 +3069,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129901093</v>
+        <v>129903311</v>
       </c>
       <c r="B21" t="n">
-        <v>92888</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457936</v>
+        <v>457721</v>
       </c>
       <c r="R21" t="n">
-        <v>6678130</v>
+        <v>6678336</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3148,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3158,7 +3154,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3297,10 +3298,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129896298</v>
+        <v>129906122</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,42 +3309,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458013</v>
+        <v>458021</v>
       </c>
       <c r="R23" t="n">
-        <v>6677834</v>
+        <v>6678149</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3372,7 +3368,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3382,12 +3378,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Barkfläk gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,10 +3410,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129906122</v>
+        <v>129903889</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,14 +3441,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458021</v>
+        <v>458004</v>
       </c>
       <c r="R24" t="n">
-        <v>6678149</v>
+        <v>6678076</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3490,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3526,45 +3517,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129903889</v>
+        <v>129901093</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>92905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458004</v>
+        <v>457936</v>
       </c>
       <c r="R25" t="n">
-        <v>6678076</v>
+        <v>6678130</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,7 +3633,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129903311</v>
+        <v>129896298</v>
       </c>
       <c r="B26" t="n">
         <v>57740</v>
@@ -3664,22 +3664,22 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457721</v>
+        <v>458013</v>
       </c>
       <c r="R26" t="n">
-        <v>6678336</v>
+        <v>6677834</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3753,7 +3753,7 @@
         <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129905534</v>
+        <v>129906012</v>
       </c>
       <c r="B28" t="n">
-        <v>81073</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458192</v>
+        <v>458056</v>
       </c>
       <c r="R28" t="n">
-        <v>6678014</v>
+        <v>6678145</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129906012</v>
+        <v>129903332</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3995,14 +3995,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458056</v>
+        <v>457738</v>
       </c>
       <c r="R29" t="n">
-        <v>6678145</v>
+        <v>6678344</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903332</v>
+        <v>129904258</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4102,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457738</v>
+        <v>458060</v>
       </c>
       <c r="R30" t="n">
-        <v>6678344</v>
+        <v>6677965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129904258</v>
+        <v>129903137</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4189,34 +4189,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458060</v>
+        <v>457711</v>
       </c>
       <c r="R31" t="n">
-        <v>6677965</v>
+        <v>6678336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4258,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4285,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129903137</v>
+        <v>129905534</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>81074</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4296,34 +4301,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457711</v>
+        <v>458192</v>
       </c>
       <c r="R32" t="n">
-        <v>6678336</v>
+        <v>6678014</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4365,12 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>129896625</v>
       </c>
       <c r="B34" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129905898</v>
+        <v>129901643</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,34 +4739,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458188</v>
+        <v>457875</v>
       </c>
       <c r="R36" t="n">
-        <v>6678089</v>
+        <v>6678186</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4798,7 +4803,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4808,7 +4813,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129903495</v>
+        <v>129905898</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4866,14 +4876,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457854</v>
+        <v>458188</v>
       </c>
       <c r="R37" t="n">
-        <v>6678241</v>
+        <v>6678089</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4905,7 +4915,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4915,7 +4925,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4942,10 +4952,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129901643</v>
+        <v>129903495</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4953,39 +4963,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457875</v>
+        <v>457854</v>
       </c>
       <c r="R38" t="n">
-        <v>6678186</v>
+        <v>6678241</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5017,7 +5022,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5027,12 +5032,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,39 +5070,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R39" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5134,7 +5129,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,12 +5139,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5187,34 +5177,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R40" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5246,7 +5241,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5256,7 +5251,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5403,7 +5403,7 @@
         <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>129895810</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>129905906</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129903770</v>
+        <v>129895784</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,34 +5746,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R45" t="n">
-        <v>6678120</v>
+        <v>6677984</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5815,7 +5820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5842,7 +5852,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129903632</v>
+        <v>129896481</v>
       </c>
       <c r="B46" t="n">
         <v>57740</v>
@@ -5873,19 +5883,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R46" t="n">
-        <v>6678255</v>
+        <v>6677968</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5917,7 +5927,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5927,12 +5937,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,7 +5969,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B47" t="n">
         <v>57740</v>
@@ -5995,14 +6005,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R47" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6044,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6054,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,10 +6086,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129896481</v>
+        <v>129903770</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6087,29 +6097,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6119,7 +6124,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6677968</v>
+        <v>6678120</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6156,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6166,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129904248</v>
+        <v>129906281</v>
       </c>
       <c r="B51" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,34 +6438,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458070</v>
+        <v>457937</v>
       </c>
       <c r="R51" t="n">
-        <v>6677915</v>
+        <v>6678260</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6507,7 +6512,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,10 +6544,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904261</v>
+        <v>129904248</v>
       </c>
       <c r="B52" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,10 +6579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458060</v>
+        <v>458070</v>
       </c>
       <c r="R52" t="n">
-        <v>6677965</v>
+        <v>6677915</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6604,7 +6614,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6614,7 +6624,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6641,10 +6651,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129906281</v>
+        <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6652,39 +6662,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457937</v>
+        <v>458060</v>
       </c>
       <c r="R53" t="n">
-        <v>6678260</v>
+        <v>6677965</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6716,7 +6721,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6726,12 +6731,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6761,7 +6761,7 @@
         <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129905893</v>
+        <v>129895750</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,34 +6997,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458190</v>
+        <v>457776</v>
       </c>
       <c r="R56" t="n">
-        <v>6678079</v>
+        <v>6677988</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7066,7 +7071,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7093,7 +7103,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129895750</v>
+        <v>129903904</v>
       </c>
       <c r="B57" t="n">
         <v>57740</v>
@@ -7133,10 +7143,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457776</v>
+        <v>458009</v>
       </c>
       <c r="R57" t="n">
-        <v>6677988</v>
+        <v>6678073</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7168,7 +7178,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7178,12 +7188,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,10 +7220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129903904</v>
+        <v>129905893</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,39 +7231,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458009</v>
+        <v>458190</v>
       </c>
       <c r="R58" t="n">
-        <v>6678073</v>
+        <v>6678079</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7290,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +7300,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129904077</v>
+        <v>129896775</v>
       </c>
       <c r="B59" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,39 +7338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458047</v>
+        <v>457962</v>
       </c>
       <c r="R59" t="n">
-        <v>6677984</v>
+        <v>6678074</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7402,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7412,12 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7444,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129896775</v>
+        <v>129904077</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,34 +7445,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457962</v>
+        <v>458047</v>
       </c>
       <c r="R60" t="n">
-        <v>6678074</v>
+        <v>6677984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7514,7 +7509,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7524,7 +7519,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7554,7 +7554,7 @@
         <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>129895673</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>129903802</v>
       </c>
       <c r="B64" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>129903740</v>
       </c>
       <c r="B65" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8203,50 +8203,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>91587</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,12 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8320,45 +8310,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895578</v>
       </c>
       <c r="B68" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457678</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678274</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8385,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8395,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8430,7 +8430,7 @@
         <v>129895677</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129896565</v>
+        <v>129901758</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457928</v>
+        <v>457814</v>
       </c>
       <c r="R70" t="n">
-        <v>6678006</v>
+        <v>6678274</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129901758</v>
+        <v>129904132</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457814</v>
+        <v>458061</v>
       </c>
       <c r="R71" t="n">
-        <v>6678274</v>
+        <v>6677989</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129904132</v>
+        <v>129896565</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458061</v>
+        <v>457928</v>
       </c>
       <c r="R72" t="n">
-        <v>6677989</v>
+        <v>6678006</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129900516</v>
+        <v>129895801</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457915</v>
+        <v>457826</v>
       </c>
       <c r="R73" t="n">
-        <v>6678101</v>
+        <v>6678001</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129901768</v>
+        <v>129900516</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457765</v>
+        <v>457915</v>
       </c>
       <c r="R74" t="n">
-        <v>6678299</v>
+        <v>6678101</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129895801</v>
+        <v>129901768</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457826</v>
+        <v>457765</v>
       </c>
       <c r="R75" t="n">
-        <v>6678001</v>
+        <v>6678299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9179,7 +9179,7 @@
         <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>89005</v>
+        <v>89022</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9283,54 +9283,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129901658</v>
+        <v>129901597</v>
       </c>
       <c r="B77" t="n">
-        <v>92888</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457862</v>
+        <v>457892</v>
       </c>
       <c r="R77" t="n">
-        <v>6678208</v>
+        <v>6678150</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9399,45 +9390,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901597</v>
+        <v>129901658</v>
       </c>
       <c r="B78" t="n">
-        <v>79088</v>
+        <v>92905</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457892</v>
+        <v>457862</v>
       </c>
       <c r="R78" t="n">
-        <v>6678150</v>
+        <v>6678208</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129903924</v>
+        <v>129896383</v>
       </c>
       <c r="B79" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458007</v>
+        <v>458001</v>
       </c>
       <c r="R79" t="n">
-        <v>6678050</v>
+        <v>6677916</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,10 +9613,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B80" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,42 +9624,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R80" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9688,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9698,12 +9693,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9730,10 +9725,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9765,13 +9760,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R81" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9795,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,7 +9805,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9837,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129896578</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9848,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457933</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678030</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129895884</v>
+        <v>129896799</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,39 +2520,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457831</v>
+        <v>457943</v>
       </c>
       <c r="R16" t="n">
-        <v>6677903</v>
+        <v>6678103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2584,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2594,12 +2589,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2626,7 +2621,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129895608</v>
+        <v>129895884</v>
       </c>
       <c r="B17" t="n">
         <v>57741</v>
@@ -2666,13 +2661,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457684</v>
+        <v>457831</v>
       </c>
       <c r="R17" t="n">
-        <v>6678274</v>
+        <v>6677903</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2711,12 +2706,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129896799</v>
+        <v>129895608</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2754,37 +2749,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457943</v>
+        <v>457684</v>
       </c>
       <c r="R18" t="n">
-        <v>6678103</v>
+        <v>6678274</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129895637</v>
+        <v>129903137</v>
       </c>
       <c r="B27" t="n">
-        <v>91603</v>
+        <v>57741</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457691</v>
+        <v>457711</v>
       </c>
       <c r="R27" t="n">
-        <v>6678174</v>
+        <v>6678336</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,48 +3862,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129905534</v>
+        <v>129895637</v>
       </c>
       <c r="B28" t="n">
-        <v>81080</v>
+        <v>91603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458192</v>
+        <v>457691</v>
       </c>
       <c r="R28" t="n">
-        <v>6678014</v>
+        <v>6678174</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,7 +3932,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3942,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3969,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129906012</v>
+        <v>129905534</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>81080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,21 +3980,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3999,10 +4004,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458056</v>
+        <v>458192</v>
       </c>
       <c r="R29" t="n">
-        <v>6678145</v>
+        <v>6678014</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4039,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4049,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4076,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129903332</v>
+        <v>129906012</v>
       </c>
       <c r="B30" t="n">
         <v>79095</v>
@@ -4102,14 +4107,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457738</v>
+        <v>458056</v>
       </c>
       <c r="R30" t="n">
-        <v>6678344</v>
+        <v>6678145</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4146,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4156,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,7 +4183,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129904258</v>
+        <v>129903332</v>
       </c>
       <c r="B31" t="n">
         <v>79095</v>
@@ -4209,14 +4214,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458060</v>
+        <v>457738</v>
       </c>
       <c r="R31" t="n">
-        <v>6677965</v>
+        <v>6678344</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4248,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4285,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129903137</v>
+        <v>129904258</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4296,34 +4301,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457711</v>
+        <v>458060</v>
       </c>
       <c r="R32" t="n">
-        <v>6678336</v>
+        <v>6677965</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4365,12 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5283,38 +5283,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>92921</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5323,10 +5327,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R41" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5368,12 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,42 +5399,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B42" t="n">
-        <v>92921</v>
+        <v>57741</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R42" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5479,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,7 +5484,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129906281</v>
+        <v>129904248</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,39 +6438,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457937</v>
+        <v>458070</v>
       </c>
       <c r="R51" t="n">
-        <v>6678260</v>
+        <v>6677915</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,7 +6497,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,12 +6507,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6544,7 +6534,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904248</v>
+        <v>129904261</v>
       </c>
       <c r="B52" t="n">
         <v>78852</v>
@@ -6579,10 +6569,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458070</v>
+        <v>458060</v>
       </c>
       <c r="R52" t="n">
-        <v>6677915</v>
+        <v>6677965</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6614,7 +6604,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6624,7 +6614,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6651,10 +6641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129904261</v>
+        <v>129906281</v>
       </c>
       <c r="B53" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6662,34 +6652,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458060</v>
+        <v>457937</v>
       </c>
       <c r="R53" t="n">
-        <v>6677965</v>
+        <v>6678260</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6721,7 +6716,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6731,7 +6726,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7327,7 +7327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129896775</v>
+        <v>129901759</v>
       </c>
       <c r="B59" t="n">
         <v>79095</v>
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457962</v>
+        <v>457813</v>
       </c>
       <c r="R59" t="n">
-        <v>6678074</v>
+        <v>6678274</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,7 +7434,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129901759</v>
+        <v>129896775</v>
       </c>
       <c r="B60" t="n">
         <v>79095</v>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457813</v>
+        <v>457962</v>
       </c>
       <c r="R60" t="n">
-        <v>6678274</v>
+        <v>6678074</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129903137</v>
+        <v>129905534</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>81080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,34 +3761,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457711</v>
+        <v>458192</v>
       </c>
       <c r="R27" t="n">
-        <v>6678336</v>
+        <v>6678014</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,12 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129895637</v>
+        <v>129906012</v>
       </c>
       <c r="B28" t="n">
-        <v>91603</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457691</v>
+        <v>458056</v>
       </c>
       <c r="R28" t="n">
-        <v>6678174</v>
+        <v>6678145</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3932,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3942,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129905534</v>
+        <v>129903332</v>
       </c>
       <c r="B29" t="n">
-        <v>81080</v>
+        <v>79095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3980,34 +3975,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458192</v>
+        <v>457738</v>
       </c>
       <c r="R29" t="n">
-        <v>6678014</v>
+        <v>6678344</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4039,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4049,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,7 +4071,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129906012</v>
+        <v>129904258</v>
       </c>
       <c r="B30" t="n">
         <v>79095</v>
@@ -4107,14 +4102,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458056</v>
+        <v>458060</v>
       </c>
       <c r="R30" t="n">
-        <v>6678145</v>
+        <v>6677965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4146,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4156,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129903332</v>
+        <v>129903137</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4194,21 +4189,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4213,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457738</v>
+        <v>457711</v>
       </c>
       <c r="R31" t="n">
-        <v>6678344</v>
+        <v>6678336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4258,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,32 +4290,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129904258</v>
+        <v>129895637</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>91603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458060</v>
+        <v>457691</v>
       </c>
       <c r="R32" t="n">
-        <v>6677965</v>
+        <v>6678174</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129905898</v>
+        <v>129896625</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,34 +4632,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458188</v>
+        <v>457943</v>
       </c>
       <c r="R35" t="n">
-        <v>6678089</v>
+        <v>6678019</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,7 +4728,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129903495</v>
+        <v>129905898</v>
       </c>
       <c r="B36" t="n">
         <v>79095</v>
@@ -4759,14 +4759,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457854</v>
+        <v>458188</v>
       </c>
       <c r="R36" t="n">
-        <v>6678241</v>
+        <v>6678089</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,10 +4835,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129901643</v>
+        <v>129903495</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,39 +4846,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457875</v>
+        <v>457854</v>
       </c>
       <c r="R37" t="n">
-        <v>6678186</v>
+        <v>6678241</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4910,7 +4905,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4920,12 +4915,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,10 +4942,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129896625</v>
+        <v>129901643</v>
       </c>
       <c r="B38" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4963,34 +4953,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457943</v>
+        <v>457875</v>
       </c>
       <c r="R38" t="n">
-        <v>6678019</v>
+        <v>6678186</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5022,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5032,7 +5027,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5516,7 +5516,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129895810</v>
+        <v>129905906</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -5547,14 +5547,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457876</v>
+        <v>458187</v>
       </c>
       <c r="R43" t="n">
-        <v>6677971</v>
+        <v>6678088</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5596,7 +5596,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5623,7 +5628,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129905906</v>
+        <v>129895810</v>
       </c>
       <c r="B44" t="n">
         <v>79095</v>
@@ -5654,14 +5659,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458187</v>
+        <v>457876</v>
       </c>
       <c r="R44" t="n">
-        <v>6678088</v>
+        <v>6677971</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5693,7 +5698,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5703,12 +5708,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 draperade tallar.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129904248</v>
+        <v>129906281</v>
       </c>
       <c r="B51" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,34 +6438,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458070</v>
+        <v>457937</v>
       </c>
       <c r="R51" t="n">
-        <v>6677915</v>
+        <v>6678260</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6507,7 +6512,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,7 +6544,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904261</v>
+        <v>129904248</v>
       </c>
       <c r="B52" t="n">
         <v>78852</v>
@@ -6569,10 +6579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458060</v>
+        <v>458070</v>
       </c>
       <c r="R52" t="n">
-        <v>6677965</v>
+        <v>6677915</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6604,7 +6614,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6614,7 +6624,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6641,10 +6651,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129906281</v>
+        <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6652,39 +6662,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457937</v>
+        <v>458060</v>
       </c>
       <c r="R53" t="n">
-        <v>6678260</v>
+        <v>6677965</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6716,7 +6721,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6726,12 +6731,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7327,7 +7327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129901759</v>
+        <v>129896775</v>
       </c>
       <c r="B59" t="n">
         <v>79095</v>
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457813</v>
+        <v>457962</v>
       </c>
       <c r="R59" t="n">
-        <v>6678274</v>
+        <v>6678074</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,7 +7434,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129896775</v>
+        <v>129901759</v>
       </c>
       <c r="B60" t="n">
         <v>79095</v>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457962</v>
+        <v>457813</v>
       </c>
       <c r="R60" t="n">
-        <v>6678074</v>
+        <v>6678274</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8534,7 +8534,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129901758</v>
+        <v>129896565</v>
       </c>
       <c r="B70" t="n">
         <v>79095</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R70" t="n">
-        <v>6678274</v>
+        <v>6678006</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129904132</v>
+        <v>129901758</v>
       </c>
       <c r="B71" t="n">
         <v>79095</v>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458061</v>
+        <v>457814</v>
       </c>
       <c r="R71" t="n">
-        <v>6677989</v>
+        <v>6678274</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129896565</v>
+        <v>129904132</v>
       </c>
       <c r="B72" t="n">
         <v>79095</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457928</v>
+        <v>458061</v>
       </c>
       <c r="R72" t="n">
-        <v>6678006</v>
+        <v>6677989</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9176,10 +9176,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901597</v>
+        <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,34 +9187,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457892</v>
+        <v>458040</v>
       </c>
       <c r="R76" t="n">
-        <v>6678150</v>
+        <v>6678171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9283,45 +9283,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129906105</v>
+        <v>129901658</v>
       </c>
       <c r="B77" t="n">
-        <v>89038</v>
+        <v>92921</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458040</v>
+        <v>457862</v>
       </c>
       <c r="R77" t="n">
-        <v>6678171</v>
+        <v>6678208</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9390,54 +9399,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901658</v>
+        <v>129901597</v>
       </c>
       <c r="B78" t="n">
-        <v>92921</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457862</v>
+        <v>457892</v>
       </c>
       <c r="R78" t="n">
-        <v>6678208</v>
+        <v>6678150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,7 +2509,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896799</v>
+        <v>129906213</v>
       </c>
       <c r="B16" t="n">
         <v>79095</v>
@@ -2540,14 +2540,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457943</v>
+        <v>457973</v>
       </c>
       <c r="R16" t="n">
-        <v>6678103</v>
+        <v>6678187</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2589,12 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2621,10 +2616,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129895884</v>
+        <v>129903410</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2632,39 +2627,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457831</v>
+        <v>457802</v>
       </c>
       <c r="R17" t="n">
-        <v>6677903</v>
+        <v>6678361</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2696,7 +2686,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2706,12 +2696,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2738,10 +2723,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129895608</v>
+        <v>129896799</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,42 +2734,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457684</v>
+        <v>457943</v>
       </c>
       <c r="R18" t="n">
-        <v>6678274</v>
+        <v>6678103</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2813,7 +2793,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,12 +2803,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2855,10 +2835,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129906213</v>
+        <v>129895884</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,34 +2846,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457973</v>
+        <v>457831</v>
       </c>
       <c r="R19" t="n">
-        <v>6678187</v>
+        <v>6677903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2925,7 +2910,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2935,7 +2920,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,10 +2952,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129903410</v>
+        <v>129895608</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,37 +2963,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457802</v>
+        <v>457684</v>
       </c>
       <c r="R20" t="n">
-        <v>6678361</v>
+        <v>6678274</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896298</v>
+        <v>129896363</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458013</v>
+        <v>458038</v>
       </c>
       <c r="R21" t="n">
-        <v>6677834</v>
+        <v>6677894</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,12 +3154,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3186,42 +3181,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129901093</v>
+        <v>129896298</v>
       </c>
       <c r="B22" t="n">
-        <v>92921</v>
+        <v>57741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3230,13 +3221,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457936</v>
+        <v>458013</v>
       </c>
       <c r="R22" t="n">
-        <v>6678130</v>
+        <v>6677834</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3265,7 +3256,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3275,7 +3266,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3302,45 +3298,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129906122</v>
+        <v>129901093</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>92923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458021</v>
+        <v>457936</v>
       </c>
       <c r="R23" t="n">
-        <v>6678149</v>
+        <v>6678130</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3372,7 +3377,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3382,12 +3387,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3414,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129903889</v>
+        <v>129906122</v>
       </c>
       <c r="B24" t="n">
         <v>79095</v>
@@ -3445,14 +3445,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458004</v>
+        <v>458021</v>
       </c>
       <c r="R24" t="n">
-        <v>6678076</v>
+        <v>6678149</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,7 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129896363</v>
+        <v>129903889</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3532,39 +3537,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458038</v>
+        <v>458004</v>
       </c>
       <c r="R25" t="n">
-        <v>6677894</v>
+        <v>6678076</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129905534</v>
+        <v>129906012</v>
       </c>
       <c r="B27" t="n">
-        <v>81080</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458192</v>
+        <v>458056</v>
       </c>
       <c r="R27" t="n">
-        <v>6678014</v>
+        <v>6678145</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129906012</v>
+        <v>129895637</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>91605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458056</v>
+        <v>457691</v>
       </c>
       <c r="R28" t="n">
-        <v>6678145</v>
+        <v>6678174</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903332</v>
+        <v>129905534</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>81080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,34 +3975,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457738</v>
+        <v>458192</v>
       </c>
       <c r="R29" t="n">
-        <v>6678344</v>
+        <v>6678014</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129904258</v>
+        <v>129903137</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4082,34 +4082,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458060</v>
+        <v>457711</v>
       </c>
       <c r="R30" t="n">
-        <v>6677965</v>
+        <v>6678336</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +4151,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129903137</v>
+        <v>129903332</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4189,21 +4194,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457711</v>
+        <v>457738</v>
       </c>
       <c r="R31" t="n">
-        <v>6678336</v>
+        <v>6678344</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4248,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,12 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,32 +4290,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129895637</v>
+        <v>129904258</v>
       </c>
       <c r="B32" t="n">
-        <v>91603</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457691</v>
+        <v>458060</v>
       </c>
       <c r="R32" t="n">
-        <v>6678174</v>
+        <v>6677965</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4504,7 +4504,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B34" t="n">
         <v>57741</v>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R34" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129896625</v>
+        <v>129905898</v>
       </c>
       <c r="B35" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,34 +4632,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457943</v>
+        <v>458188</v>
       </c>
       <c r="R35" t="n">
-        <v>6678019</v>
+        <v>6678089</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,7 +4728,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129905898</v>
+        <v>129903495</v>
       </c>
       <c r="B36" t="n">
         <v>79095</v>
@@ -4759,14 +4759,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458188</v>
+        <v>457854</v>
       </c>
       <c r="R36" t="n">
-        <v>6678089</v>
+        <v>6678241</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,10 +4835,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129903495</v>
+        <v>129896625</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,21 +4846,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457854</v>
+        <v>457943</v>
       </c>
       <c r="R37" t="n">
-        <v>6678241</v>
+        <v>6678019</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4942,7 +4942,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129901643</v>
+        <v>129895788</v>
       </c>
       <c r="B38" t="n">
         <v>57741</v>
@@ -4973,7 +4973,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457875</v>
+        <v>457819</v>
       </c>
       <c r="R38" t="n">
-        <v>6678186</v>
+        <v>6677981</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5286,7 +5286,7 @@
         <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129896481</v>
+        <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,29 +5746,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -5778,7 +5773,7 @@
         <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6677968</v>
+        <v>6678120</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5815,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5969,10 +5959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903770</v>
+        <v>129895784</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5980,34 +5970,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R47" t="n">
-        <v>6678120</v>
+        <v>6677984</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6039,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6049,7 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,7 +6076,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129895784</v>
+        <v>129896481</v>
       </c>
       <c r="B48" t="n">
         <v>57741</v>
@@ -6107,7 +6107,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457792</v>
+        <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6677984</v>
+        <v>6677968</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6761,7 +6761,7 @@
         <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>92957</v>
+        <v>92959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129895750</v>
+        <v>129905893</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,39 +6997,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457776</v>
+        <v>458190</v>
       </c>
       <c r="R56" t="n">
-        <v>6677988</v>
+        <v>6678079</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7061,7 +7056,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7071,12 +7066,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7103,10 +7093,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129905893</v>
+        <v>129903904</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7114,34 +7104,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458190</v>
+        <v>458009</v>
       </c>
       <c r="R57" t="n">
-        <v>6678079</v>
+        <v>6678073</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7173,7 +7168,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7183,7 +7178,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,7 +7210,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129903904</v>
+        <v>129895750</v>
       </c>
       <c r="B58" t="n">
         <v>57741</v>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458009</v>
+        <v>457776</v>
       </c>
       <c r="R58" t="n">
-        <v>6678073</v>
+        <v>6677988</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129896775</v>
+        <v>129904077</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,34 +7338,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457962</v>
+        <v>458047</v>
       </c>
       <c r="R59" t="n">
-        <v>6678074</v>
+        <v>6677984</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7402,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7412,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7541,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129904077</v>
+        <v>129896775</v>
       </c>
       <c r="B61" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,39 +7562,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458047</v>
+        <v>457962</v>
       </c>
       <c r="R61" t="n">
-        <v>6677984</v>
+        <v>6678074</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7616,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7626,12 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,7 +7658,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129895673</v>
+        <v>129903802</v>
       </c>
       <c r="B62" t="n">
         <v>79095</v>
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457806</v>
+        <v>457983</v>
       </c>
       <c r="R62" t="n">
-        <v>6678097</v>
+        <v>6678105</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129896652</v>
+        <v>129903740</v>
       </c>
       <c r="B63" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7776,39 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457954</v>
+        <v>457907</v>
       </c>
       <c r="R63" t="n">
-        <v>6678018</v>
+        <v>6678176</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7840,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7850,12 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,7 +7872,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903802</v>
+        <v>129906347</v>
       </c>
       <c r="B64" t="n">
         <v>79095</v>
@@ -7913,14 +7903,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457983</v>
+        <v>457859</v>
       </c>
       <c r="R64" t="n">
-        <v>6678105</v>
+        <v>6678305</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7942,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7952,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,7 +7979,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903740</v>
+        <v>129895673</v>
       </c>
       <c r="B65" t="n">
         <v>79095</v>
@@ -8024,13 +8014,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457907</v>
+        <v>457806</v>
       </c>
       <c r="R65" t="n">
-        <v>6678176</v>
+        <v>6678097</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,7 +8049,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8059,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129906347</v>
+        <v>129896652</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,34 +8097,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457859</v>
+        <v>457954</v>
       </c>
       <c r="R66" t="n">
-        <v>6678305</v>
+        <v>6678018</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8171,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,50 +8203,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>91605</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,12 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8320,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>91603</v>
+        <v>79095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8355,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,10 +8417,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895677</v>
+        <v>129895578</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8438,34 +8428,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457806</v>
+        <v>457678</v>
       </c>
       <c r="R69" t="n">
-        <v>6678096</v>
+        <v>6678274</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8497,7 +8492,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,7 +8502,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129895801</v>
+        <v>129900516</v>
       </c>
       <c r="B73" t="n">
         <v>79095</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457826</v>
+        <v>457915</v>
       </c>
       <c r="R73" t="n">
-        <v>6678001</v>
+        <v>6678101</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129900516</v>
+        <v>129901768</v>
       </c>
       <c r="B74" t="n">
         <v>79095</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457915</v>
+        <v>457765</v>
       </c>
       <c r="R74" t="n">
-        <v>6678101</v>
+        <v>6678299</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129901768</v>
+        <v>129895801</v>
       </c>
       <c r="B75" t="n">
         <v>79095</v>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457765</v>
+        <v>457826</v>
       </c>
       <c r="R75" t="n">
-        <v>6678299</v>
+        <v>6678001</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9286,7 +9286,7 @@
         <v>129901658</v>
       </c>
       <c r="B77" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129896383</v>
+        <v>129903924</v>
       </c>
       <c r="B79" t="n">
         <v>79095</v>
@@ -9541,13 +9541,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458001</v>
+        <v>458007</v>
       </c>
       <c r="R79" t="n">
-        <v>6677916</v>
+        <v>6678050</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9613,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129896383</v>
       </c>
       <c r="B80" t="n">
         <v>79095</v>
@@ -9648,13 +9648,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>458001</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6677916</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,12 +9693,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9725,10 +9720,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129895634</v>
+        <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9736,42 +9731,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457704</v>
+        <v>457933</v>
       </c>
       <c r="R81" t="n">
-        <v>6678154</v>
+        <v>6678030</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9790,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9800,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9842,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129906213</v>
+        <v>129895884</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,34 +2520,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457973</v>
+        <v>457831</v>
       </c>
       <c r="R16" t="n">
-        <v>6678187</v>
+        <v>6677903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2579,7 +2584,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2589,7 +2594,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,10 +2626,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129903410</v>
+        <v>129895608</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2627,37 +2637,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457802</v>
+        <v>457684</v>
       </c>
       <c r="R17" t="n">
-        <v>6678361</v>
+        <v>6678274</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2686,7 +2701,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2696,7 +2711,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,7 +2746,7 @@
         <v>129896799</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2835,10 +2855,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129895884</v>
+        <v>129906213</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2846,39 +2866,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457831</v>
+        <v>457973</v>
       </c>
       <c r="R19" t="n">
-        <v>6677903</v>
+        <v>6678187</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2910,7 +2925,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2920,12 +2935,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,10 +2962,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129895608</v>
+        <v>129903410</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2963,42 +2973,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457684</v>
+        <v>457802</v>
       </c>
       <c r="R20" t="n">
-        <v>6678274</v>
+        <v>6678361</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3037,12 +3042,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896363</v>
+        <v>129896298</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458038</v>
+        <v>458013</v>
       </c>
       <c r="R21" t="n">
-        <v>6677894</v>
+        <v>6677834</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,7 +3154,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,10 +3186,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129896298</v>
+        <v>129906122</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,42 +3197,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458013</v>
+        <v>458021</v>
       </c>
       <c r="R22" t="n">
-        <v>6677834</v>
+        <v>6678149</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Barkfläk gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3298,54 +3298,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129901093</v>
+        <v>129903889</v>
       </c>
       <c r="B23" t="n">
-        <v>92923</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457936</v>
+        <v>458004</v>
       </c>
       <c r="R23" t="n">
-        <v>6678130</v>
+        <v>6678076</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3377,7 +3368,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3387,7 +3378,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,10 +3405,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129906122</v>
+        <v>129903311</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,34 +3416,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458021</v>
+        <v>457721</v>
       </c>
       <c r="R24" t="n">
-        <v>6678149</v>
+        <v>6678336</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3490,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hänglavsrikt.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3526,45 +3522,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129903889</v>
+        <v>129901093</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>93010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458004</v>
+        <v>457936</v>
       </c>
       <c r="R25" t="n">
-        <v>6678076</v>
+        <v>6678130</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3596,7 +3601,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3611,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,10 +3638,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129903311</v>
+        <v>129896363</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,16 +3649,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3664,19 +3669,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457721</v>
+        <v>458038</v>
       </c>
       <c r="R26" t="n">
-        <v>6678336</v>
+        <v>6677894</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3708,7 +3713,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3723,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129906012</v>
+        <v>129895637</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>91692</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458056</v>
+        <v>457691</v>
       </c>
       <c r="R27" t="n">
-        <v>6678145</v>
+        <v>6678174</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129895637</v>
+        <v>129903332</v>
       </c>
       <c r="B28" t="n">
-        <v>91605</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457691</v>
+        <v>457738</v>
       </c>
       <c r="R28" t="n">
-        <v>6678174</v>
+        <v>6678344</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129905534</v>
+        <v>129904258</v>
       </c>
       <c r="B29" t="n">
-        <v>81080</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,34 +3975,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458192</v>
+        <v>458060</v>
       </c>
       <c r="R29" t="n">
-        <v>6678014</v>
+        <v>6677965</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,7 +4074,7 @@
         <v>129903137</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129903332</v>
+        <v>129905534</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>81165</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4194,34 +4194,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457738</v>
+        <v>458192</v>
       </c>
       <c r="R31" t="n">
-        <v>6678344</v>
+        <v>6678014</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129904258</v>
+        <v>129906012</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4321,14 +4321,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458060</v>
+        <v>458056</v>
       </c>
       <c r="R32" t="n">
-        <v>6677965</v>
+        <v>6678145</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129901643</v>
+        <v>129895788</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457875</v>
+        <v>457819</v>
       </c>
       <c r="R34" t="n">
-        <v>6678186</v>
+        <v>6677981</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129905898</v>
+        <v>129896625</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,34 +4632,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458188</v>
+        <v>457943</v>
       </c>
       <c r="R35" t="n">
-        <v>6678089</v>
+        <v>6678019</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129903495</v>
+        <v>129901643</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,34 +4739,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457854</v>
+        <v>457875</v>
       </c>
       <c r="R36" t="n">
-        <v>6678241</v>
+        <v>6678186</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4798,7 +4803,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4808,7 +4813,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129896625</v>
+        <v>129905898</v>
       </c>
       <c r="B37" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,34 +4856,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457943</v>
+        <v>458188</v>
       </c>
       <c r="R37" t="n">
-        <v>6678019</v>
+        <v>6678089</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4905,7 +4915,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4915,7 +4925,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4942,10 +4952,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129895788</v>
+        <v>129903495</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4953,42 +4963,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457819</v>
+        <v>457854</v>
       </c>
       <c r="R38" t="n">
-        <v>6677981</v>
+        <v>6678241</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5017,7 +5022,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5027,12 +5032,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,34 +5070,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5129,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5139,7 +5144,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,10 +5176,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,39 +5187,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R40" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5241,7 +5246,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5251,12 +5256,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5283,42 +5283,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B41" t="n">
-        <v>92923</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5327,10 +5323,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R41" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5362,7 +5358,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5368,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,38 +5400,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>93010</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R42" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,12 +5489,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129905906</v>
+        <v>129895810</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5547,14 +5547,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458187</v>
+        <v>457876</v>
       </c>
       <c r="R43" t="n">
-        <v>6678088</v>
+        <v>6677971</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5596,12 +5596,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 draperade tallar.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,10 +5623,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129895810</v>
+        <v>129905906</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5659,14 +5654,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457876</v>
+        <v>458187</v>
       </c>
       <c r="R44" t="n">
-        <v>6677971</v>
+        <v>6678088</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5698,7 +5693,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5708,7 +5703,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129903770</v>
+        <v>129895784</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,34 +5746,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457943</v>
+        <v>457792</v>
       </c>
       <c r="R45" t="n">
-        <v>6678120</v>
+        <v>6677984</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5815,7 +5820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5842,10 +5852,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129903632</v>
+        <v>129896481</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5873,19 +5883,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457937</v>
+        <v>457943</v>
       </c>
       <c r="R46" t="n">
-        <v>6678255</v>
+        <v>6677968</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5917,7 +5927,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5927,12 +5937,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,10 +5969,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129895784</v>
+        <v>129903632</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5995,14 +6005,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457792</v>
+        <v>457937</v>
       </c>
       <c r="R47" t="n">
-        <v>6677984</v>
+        <v>6678255</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6034,7 +6044,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6044,12 +6054,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,10 +6086,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129896481</v>
+        <v>129903770</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6087,29 +6097,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6119,7 +6124,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6677968</v>
+        <v>6678120</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +6156,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +6166,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6193,10 +6193,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129895622</v>
+        <v>129901694</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457689</v>
+        <v>457867</v>
       </c>
       <c r="R49" t="n">
-        <v>6678248</v>
+        <v>6678204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,10 +6310,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129901694</v>
+        <v>129895622</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457867</v>
+        <v>457689</v>
       </c>
       <c r="R50" t="n">
-        <v>6678204</v>
+        <v>6678248</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129906281</v>
+        <v>129904248</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>78937</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,39 +6438,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457937</v>
+        <v>458070</v>
       </c>
       <c r="R51" t="n">
-        <v>6678260</v>
+        <v>6677915</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,7 +6497,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,12 +6507,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6544,10 +6534,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904248</v>
+        <v>129906281</v>
       </c>
       <c r="B52" t="n">
-        <v>78852</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6555,34 +6545,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458070</v>
+        <v>457937</v>
       </c>
       <c r="R52" t="n">
-        <v>6677915</v>
+        <v>6678260</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6614,7 +6609,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6624,7 +6619,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6654,7 +6654,7 @@
         <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>92959</v>
+        <v>93046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129905893</v>
+        <v>129895750</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,34 +6997,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458190</v>
+        <v>457776</v>
       </c>
       <c r="R56" t="n">
-        <v>6678079</v>
+        <v>6677988</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7066,7 +7071,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7093,10 +7103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129903904</v>
+        <v>129905893</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7104,39 +7114,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458009</v>
+        <v>458190</v>
       </c>
       <c r="R57" t="n">
-        <v>6678073</v>
+        <v>6678079</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7168,7 +7173,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7178,12 +7183,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,10 +7210,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129895750</v>
+        <v>129903904</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457776</v>
+        <v>458009</v>
       </c>
       <c r="R58" t="n">
-        <v>6677988</v>
+        <v>6678073</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129904077</v>
+        <v>129896775</v>
       </c>
       <c r="B59" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,39 +7338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458047</v>
+        <v>457962</v>
       </c>
       <c r="R59" t="n">
-        <v>6677984</v>
+        <v>6678074</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7402,7 +7397,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7412,12 +7407,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7444,10 +7434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129901759</v>
+        <v>129904077</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,34 +7445,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457813</v>
+        <v>458047</v>
       </c>
       <c r="R60" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7514,7 +7509,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7524,7 +7519,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7551,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129896775</v>
+        <v>129901759</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457962</v>
+        <v>457813</v>
       </c>
       <c r="R61" t="n">
-        <v>6678074</v>
+        <v>6678274</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129903802</v>
+        <v>129896652</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,34 +7669,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457983</v>
+        <v>457954</v>
       </c>
       <c r="R62" t="n">
-        <v>6678105</v>
+        <v>6678018</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7728,7 +7733,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,7 +7743,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7765,10 +7775,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129903740</v>
+        <v>129895673</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7800,13 +7810,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457907</v>
+        <v>457806</v>
       </c>
       <c r="R63" t="n">
-        <v>6678176</v>
+        <v>6678097</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,7 +7845,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7845,7 +7855,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7872,10 +7882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129906347</v>
+        <v>129903802</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7903,14 +7913,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457859</v>
+        <v>457983</v>
       </c>
       <c r="R64" t="n">
-        <v>6678305</v>
+        <v>6678105</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7942,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7952,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7979,10 +7989,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129895673</v>
+        <v>129903740</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8014,13 +8024,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457806</v>
+        <v>457907</v>
       </c>
       <c r="R65" t="n">
-        <v>6678097</v>
+        <v>6678176</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8049,7 +8059,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8059,7 +8069,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8086,10 +8096,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129896652</v>
+        <v>129906347</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8097,39 +8107,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457954</v>
+        <v>457859</v>
       </c>
       <c r="R66" t="n">
-        <v>6678018</v>
+        <v>6678305</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8161,7 +8166,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8171,12 +8176,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,45 +8203,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129896274</v>
+        <v>129895578</v>
       </c>
       <c r="B67" t="n">
-        <v>91605</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458013</v>
+        <v>457678</v>
       </c>
       <c r="R67" t="n">
-        <v>6677833</v>
+        <v>6678274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8283,7 +8288,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8310,32 +8320,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129895677</v>
+        <v>129896274</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>91692</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8345,10 +8355,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457806</v>
+        <v>458013</v>
       </c>
       <c r="R68" t="n">
-        <v>6678096</v>
+        <v>6677833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8380,7 +8390,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8390,7 +8400,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8417,10 +8427,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895578</v>
+        <v>129895677</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8428,39 +8438,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457678</v>
+        <v>457806</v>
       </c>
       <c r="R69" t="n">
-        <v>6678274</v>
+        <v>6678096</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8492,7 +8497,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8502,12 +8507,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8537,7 +8537,7 @@
         <v>129896565</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>129901758</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>129904132</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>129900516</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>129901768</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>129895801</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129906105</v>
+        <v>129901597</v>
       </c>
       <c r="B76" t="n">
-        <v>89038</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,34 +9187,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458040</v>
+        <v>457892</v>
       </c>
       <c r="R76" t="n">
-        <v>6678171</v>
+        <v>6678150</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9286,7 +9286,7 @@
         <v>129901658</v>
       </c>
       <c r="B77" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129901597</v>
+        <v>129906105</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>89125</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9410,34 +9410,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457892</v>
+        <v>458040</v>
       </c>
       <c r="R78" t="n">
-        <v>6678150</v>
+        <v>6678171</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9517,37 +9517,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R79" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9581,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,7 +9591,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9616,7 +9626,7 @@
         <v>129896383</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9723,7 +9733,7 @@
         <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9832,10 +9842,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129895634</v>
+        <v>129903924</v>
       </c>
       <c r="B82" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9843,42 +9853,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457704</v>
+        <v>458007</v>
       </c>
       <c r="R82" t="n">
-        <v>6678154</v>
+        <v>6678050</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9907,7 +9912,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9917,12 +9922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896298</v>
+        <v>129906122</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,42 +3080,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458013</v>
+        <v>458021</v>
       </c>
       <c r="R21" t="n">
-        <v>6677834</v>
+        <v>6678149</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3154,12 +3149,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Barkfläk gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3186,7 +3181,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129906122</v>
+        <v>129903889</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3217,14 +3212,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458021</v>
+        <v>458004</v>
       </c>
       <c r="R22" t="n">
-        <v>6678149</v>
+        <v>6678076</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3266,12 +3261,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3298,10 +3288,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129903889</v>
+        <v>129903311</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,34 +3299,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458004</v>
+        <v>457721</v>
       </c>
       <c r="R23" t="n">
-        <v>6678076</v>
+        <v>6678336</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3368,7 +3363,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3378,7 +3373,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,50 +3405,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129903311</v>
+        <v>129901093</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>93010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457721</v>
+        <v>457936</v>
       </c>
       <c r="R24" t="n">
-        <v>6678336</v>
+        <v>6678130</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3480,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3490,12 +3494,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3522,42 +3521,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129901093</v>
+        <v>129896363</v>
       </c>
       <c r="B25" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3566,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457936</v>
+        <v>458038</v>
       </c>
       <c r="R25" t="n">
-        <v>6678130</v>
+        <v>6677894</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3601,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3611,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3638,10 +3633,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129896363</v>
+        <v>129896298</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3649,16 +3644,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3678,13 +3673,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458038</v>
+        <v>458013</v>
       </c>
       <c r="R26" t="n">
-        <v>6677894</v>
+        <v>6677834</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3713,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3723,7 +3718,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129901694</v>
+        <v>129895622</v>
       </c>
       <c r="B49" t="n">
         <v>57826</v>
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457867</v>
+        <v>457689</v>
       </c>
       <c r="R49" t="n">
-        <v>6678204</v>
+        <v>6678248</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,7 +6310,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129895622</v>
+        <v>129901694</v>
       </c>
       <c r="B50" t="n">
         <v>57826</v>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457689</v>
+        <v>457867</v>
       </c>
       <c r="R50" t="n">
-        <v>6678248</v>
+        <v>6678204</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -5283,38 +5283,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129896531</v>
+        <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>93010</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5323,10 +5327,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457940</v>
+        <v>457857</v>
       </c>
       <c r="R41" t="n">
-        <v>6677971</v>
+        <v>6678215</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5368,12 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,42 +5399,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129901703</v>
+        <v>129896531</v>
       </c>
       <c r="B42" t="n">
-        <v>93010</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457857</v>
+        <v>457940</v>
       </c>
       <c r="R42" t="n">
-        <v>6678215</v>
+        <v>6677971</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5479,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,7 +5484,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129895622</v>
+        <v>129901694</v>
       </c>
       <c r="B49" t="n">
         <v>57826</v>
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457689</v>
+        <v>457867</v>
       </c>
       <c r="R49" t="n">
-        <v>6678248</v>
+        <v>6678204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,7 +6310,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129901694</v>
+        <v>129895622</v>
       </c>
       <c r="B50" t="n">
         <v>57826</v>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457867</v>
+        <v>457689</v>
       </c>
       <c r="R50" t="n">
-        <v>6678204</v>
+        <v>6678248</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129901758</v>
+        <v>129904132</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457814</v>
+        <v>458061</v>
       </c>
       <c r="R71" t="n">
-        <v>6678274</v>
+        <v>6677989</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,7 +8748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129904132</v>
+        <v>129901758</v>
       </c>
       <c r="B72" t="n">
         <v>79180</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458061</v>
+        <v>457814</v>
       </c>
       <c r="R72" t="n">
-        <v>6677989</v>
+        <v>6678274</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129900516</v>
+        <v>129895801</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457915</v>
+        <v>457826</v>
       </c>
       <c r="R73" t="n">
-        <v>6678101</v>
+        <v>6678001</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129901768</v>
+        <v>129900516</v>
       </c>
       <c r="B74" t="n">
         <v>79180</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457765</v>
+        <v>457915</v>
       </c>
       <c r="R74" t="n">
-        <v>6678299</v>
+        <v>6678101</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129895801</v>
+        <v>129901768</v>
       </c>
       <c r="B75" t="n">
         <v>79180</v>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457826</v>
+        <v>457765</v>
       </c>
       <c r="R75" t="n">
-        <v>6678001</v>
+        <v>6678299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129895884</v>
+        <v>129906213</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,39 +2520,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457831</v>
+        <v>457973</v>
       </c>
       <c r="R16" t="n">
-        <v>6677903</v>
+        <v>6678187</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2584,7 +2579,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2594,12 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2626,10 +2616,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129895608</v>
+        <v>129903410</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2637,42 +2627,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457684</v>
+        <v>457802</v>
       </c>
       <c r="R17" t="n">
-        <v>6678274</v>
+        <v>6678361</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,7 +2686,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2711,12 +2696,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2726,7 @@
         <v>129896799</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2855,10 +2835,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129906213</v>
+        <v>129895884</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,34 +2846,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457973</v>
+        <v>457831</v>
       </c>
       <c r="R19" t="n">
-        <v>6678187</v>
+        <v>6677903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2925,7 +2910,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2935,7 +2920,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,10 +2952,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129903410</v>
+        <v>129895608</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,37 +2963,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457802</v>
+        <v>457684</v>
       </c>
       <c r="R20" t="n">
-        <v>6678361</v>
+        <v>6678274</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3042,7 +3037,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129906122</v>
+        <v>129896363</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3080,34 +3080,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458021</v>
+        <v>458038</v>
       </c>
       <c r="R21" t="n">
-        <v>6678149</v>
+        <v>6677894</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,12 +3154,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129903889</v>
+        <v>129896298</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,37 +3192,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458004</v>
+        <v>458013</v>
       </c>
       <c r="R22" t="n">
-        <v>6678076</v>
+        <v>6677834</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3261,14 +3266,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3288,50 +3298,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129903311</v>
+        <v>129901093</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>92923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457721</v>
+        <v>457936</v>
       </c>
       <c r="R23" t="n">
-        <v>6678336</v>
+        <v>6678130</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3363,7 +3377,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3373,12 +3387,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,54 +3414,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129901093</v>
+        <v>129906122</v>
       </c>
       <c r="B24" t="n">
-        <v>93010</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457936</v>
+        <v>458021</v>
       </c>
       <c r="R24" t="n">
-        <v>6678130</v>
+        <v>6678149</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,7 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129896363</v>
+        <v>129903889</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3532,39 +3537,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458038</v>
+        <v>458004</v>
       </c>
       <c r="R25" t="n">
-        <v>6677894</v>
+        <v>6678076</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,10 +3633,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129896298</v>
+        <v>129903311</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,22 +3664,22 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458013</v>
+        <v>457721</v>
       </c>
       <c r="R26" t="n">
-        <v>6677834</v>
+        <v>6678336</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Barkfläk gran.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,48 +3750,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129895637</v>
+        <v>129906012</v>
       </c>
       <c r="B27" t="n">
-        <v>91692</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457691</v>
+        <v>458056</v>
       </c>
       <c r="R27" t="n">
-        <v>6678174</v>
+        <v>6678145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,48 +3857,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129903332</v>
+        <v>129895637</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>91605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457738</v>
+        <v>457691</v>
       </c>
       <c r="R28" t="n">
-        <v>6678344</v>
+        <v>6678174</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129904258</v>
+        <v>129905534</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>81080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,34 +3975,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458060</v>
+        <v>458192</v>
       </c>
       <c r="R29" t="n">
-        <v>6677965</v>
+        <v>6678014</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,7 +4074,7 @@
         <v>129903137</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4183,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129905534</v>
+        <v>129903332</v>
       </c>
       <c r="B31" t="n">
-        <v>81165</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4194,34 +4194,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458192</v>
+        <v>457738</v>
       </c>
       <c r="R31" t="n">
-        <v>6678014</v>
+        <v>6678344</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,10 +4290,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129906012</v>
+        <v>129904258</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4321,14 +4321,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458056</v>
+        <v>458060</v>
       </c>
       <c r="R32" t="n">
-        <v>6678145</v>
+        <v>6677965</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,7 +4400,7 @@
         <v>129896809</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129895788</v>
+        <v>129901643</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457819</v>
+        <v>457875</v>
       </c>
       <c r="R34" t="n">
-        <v>6677981</v>
+        <v>6678186</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129896625</v>
+        <v>129905898</v>
       </c>
       <c r="B35" t="n">
-        <v>91728</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,34 +4632,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457943</v>
+        <v>458188</v>
       </c>
       <c r="R35" t="n">
-        <v>6678019</v>
+        <v>6678089</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129901643</v>
+        <v>129903495</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,39 +4739,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457875</v>
+        <v>457854</v>
       </c>
       <c r="R36" t="n">
-        <v>6678186</v>
+        <v>6678241</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4803,7 +4798,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4813,12 +4808,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4845,10 +4835,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129905898</v>
+        <v>129896625</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>91641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,34 +4846,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458188</v>
+        <v>457943</v>
       </c>
       <c r="R37" t="n">
-        <v>6678089</v>
+        <v>6678019</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4915,7 +4905,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4925,7 +4915,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,10 +4942,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129903495</v>
+        <v>129895788</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4963,37 +4953,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457854</v>
+        <v>457819</v>
       </c>
       <c r="R38" t="n">
-        <v>6678241</v>
+        <v>6677981</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5022,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5032,7 +5027,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896716</v>
+        <v>129896559</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,39 +5070,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457951</v>
+        <v>457931</v>
       </c>
       <c r="R39" t="n">
-        <v>6678037</v>
+        <v>6678011</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5134,7 +5129,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,12 +5139,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896559</v>
+        <v>129896716</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5187,34 +5177,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457931</v>
+        <v>457951</v>
       </c>
       <c r="R40" t="n">
-        <v>6678011</v>
+        <v>6678037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5246,7 +5241,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5256,7 +5251,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5286,7 +5286,7 @@
         <v>129901703</v>
       </c>
       <c r="B41" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>129896531</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129895810</v>
+        <v>129905906</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5547,14 +5547,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457876</v>
+        <v>458187</v>
       </c>
       <c r="R43" t="n">
-        <v>6677971</v>
+        <v>6678088</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5596,7 +5596,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5623,10 +5628,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129905906</v>
+        <v>129895810</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5654,14 +5659,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458187</v>
+        <v>457876</v>
       </c>
       <c r="R44" t="n">
-        <v>6678088</v>
+        <v>6677971</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5693,7 +5698,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5703,12 +5708,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 draperade tallar.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129895784</v>
+        <v>129903770</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,39 +5746,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457792</v>
+        <v>457943</v>
       </c>
       <c r="R45" t="n">
-        <v>6677984</v>
+        <v>6678120</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5815,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5852,10 +5842,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129896481</v>
+        <v>129903632</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5883,19 +5873,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457943</v>
+        <v>457937</v>
       </c>
       <c r="R46" t="n">
-        <v>6677968</v>
+        <v>6678255</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5927,7 +5917,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5937,12 +5927,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5969,10 +5959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903632</v>
+        <v>129895784</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6005,14 +5995,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457937</v>
+        <v>457792</v>
       </c>
       <c r="R47" t="n">
-        <v>6678255</v>
+        <v>6677984</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6044,7 +6034,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6054,12 +6044,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6086,10 +6076,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129903770</v>
+        <v>129896481</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6097,24 +6087,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
@@ -6124,7 +6119,7 @@
         <v>457943</v>
       </c>
       <c r="R48" t="n">
-        <v>6678120</v>
+        <v>6677968</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6156,7 +6151,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6166,7 +6161,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6193,10 +6193,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129901694</v>
+        <v>129895622</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457867</v>
+        <v>457689</v>
       </c>
       <c r="R49" t="n">
-        <v>6678204</v>
+        <v>6678248</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,10 +6310,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129895622</v>
+        <v>129901694</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457689</v>
+        <v>457867</v>
       </c>
       <c r="R50" t="n">
-        <v>6678248</v>
+        <v>6678204</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,19 +6395,19 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129904248</v>
+        <v>129906281</v>
       </c>
       <c r="B51" t="n">
-        <v>78937</v>
+        <v>57741</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,34 +6438,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458070</v>
+        <v>457937</v>
       </c>
       <c r="R51" t="n">
-        <v>6677915</v>
+        <v>6678260</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6507,7 +6512,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,10 +6544,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129906281</v>
+        <v>129904248</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>78852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6545,39 +6555,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457937</v>
+        <v>458070</v>
       </c>
       <c r="R52" t="n">
-        <v>6678260</v>
+        <v>6677915</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6609,7 +6614,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6619,12 +6624,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6654,7 +6654,7 @@
         <v>129904261</v>
       </c>
       <c r="B53" t="n">
-        <v>78937</v>
+        <v>78852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>129895861</v>
       </c>
       <c r="B54" t="n">
-        <v>93046</v>
+        <v>92959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>129896461</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129895750</v>
+        <v>129905893</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,39 +6997,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457776</v>
+        <v>458190</v>
       </c>
       <c r="R56" t="n">
-        <v>6677988</v>
+        <v>6678079</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7061,7 +7056,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7071,12 +7066,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7103,10 +7093,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129905893</v>
+        <v>129903904</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7114,34 +7104,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458190</v>
+        <v>458009</v>
       </c>
       <c r="R57" t="n">
-        <v>6678079</v>
+        <v>6678073</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7173,7 +7168,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7183,7 +7178,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,10 +7210,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129903904</v>
+        <v>129895750</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458009</v>
+        <v>457776</v>
       </c>
       <c r="R58" t="n">
-        <v>6678073</v>
+        <v>6677988</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,19 +7295,19 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG58" t="b">
         <v>0</v>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129896775</v>
+        <v>129904077</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,34 +7338,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457962</v>
+        <v>458047</v>
       </c>
       <c r="R59" t="n">
-        <v>6678074</v>
+        <v>6677984</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7402,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7412,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,10 +7444,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129904077</v>
+        <v>129901759</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,39 +7455,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458047</v>
+        <v>457813</v>
       </c>
       <c r="R60" t="n">
-        <v>6677984</v>
+        <v>6678274</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7509,7 +7514,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7519,12 +7524,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7551,10 +7551,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129901759</v>
+        <v>129896775</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457813</v>
+        <v>457962</v>
       </c>
       <c r="R61" t="n">
-        <v>6678274</v>
+        <v>6678074</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7658,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129896652</v>
+        <v>129903802</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,39 +7669,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457954</v>
+        <v>457983</v>
       </c>
       <c r="R62" t="n">
-        <v>6678018</v>
+        <v>6678105</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7733,7 +7728,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7743,12 +7738,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7775,10 +7765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129895673</v>
+        <v>129903740</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7810,13 +7800,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457806</v>
+        <v>457907</v>
       </c>
       <c r="R63" t="n">
-        <v>6678097</v>
+        <v>6678176</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7845,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7855,7 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,10 +7872,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903802</v>
+        <v>129906347</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7913,14 +7903,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457983</v>
+        <v>457859</v>
       </c>
       <c r="R64" t="n">
-        <v>6678105</v>
+        <v>6678305</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7942,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7952,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,10 +7979,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903740</v>
+        <v>129895673</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8024,13 +8014,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457907</v>
+        <v>457806</v>
       </c>
       <c r="R65" t="n">
-        <v>6678176</v>
+        <v>6678097</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,7 +8049,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +8059,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +8086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129906347</v>
+        <v>129896652</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,34 +8097,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457859</v>
+        <v>457954</v>
       </c>
       <c r="R66" t="n">
-        <v>6678305</v>
+        <v>6678018</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +8171,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,50 +8203,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129896274</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>91605</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>458013</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6677833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,12 +8283,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8320,32 +8310,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895677</v>
       </c>
       <c r="B68" t="n">
-        <v>91692</v>
+        <v>79095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8355,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8380,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8390,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,10 +8417,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895677</v>
+        <v>129895578</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8438,34 +8428,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457806</v>
+        <v>457678</v>
       </c>
       <c r="R69" t="n">
-        <v>6678096</v>
+        <v>6678274</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8497,7 +8492,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,7 +8502,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8537,7 +8537,7 @@
         <v>129896565</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129904132</v>
+        <v>129901758</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458061</v>
+        <v>457814</v>
       </c>
       <c r="R71" t="n">
-        <v>6677989</v>
+        <v>6678274</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129901758</v>
+        <v>129904132</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457814</v>
+        <v>458061</v>
       </c>
       <c r="R72" t="n">
-        <v>6678274</v>
+        <v>6677989</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129895801</v>
+        <v>129900516</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457826</v>
+        <v>457915</v>
       </c>
       <c r="R73" t="n">
-        <v>6678001</v>
+        <v>6678101</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129900516</v>
+        <v>129901768</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457915</v>
+        <v>457765</v>
       </c>
       <c r="R74" t="n">
-        <v>6678101</v>
+        <v>6678299</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129901768</v>
+        <v>129895801</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457765</v>
+        <v>457826</v>
       </c>
       <c r="R75" t="n">
-        <v>6678299</v>
+        <v>6678001</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,10 +9176,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901597</v>
+        <v>129906105</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>89038</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,34 +9187,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457892</v>
+        <v>458040</v>
       </c>
       <c r="R76" t="n">
-        <v>6678150</v>
+        <v>6678171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,14 +9256,14 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>129901658</v>
       </c>
       <c r="B77" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129906105</v>
+        <v>129901597</v>
       </c>
       <c r="B78" t="n">
-        <v>89125</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9410,34 +9410,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458040</v>
+        <v>457892</v>
       </c>
       <c r="R78" t="n">
-        <v>6678171</v>
+        <v>6678150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129895634</v>
+        <v>129903924</v>
       </c>
       <c r="B79" t="n">
-        <v>57826</v>
+        <v>79095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9517,42 +9517,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457704</v>
+        <v>458007</v>
       </c>
       <c r="R79" t="n">
-        <v>6678154</v>
+        <v>6678050</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9581,7 +9576,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9591,12 +9586,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9626,7 +9616,7 @@
         <v>129896383</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9733,7 +9723,7 @@
         <v>129896578</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9842,10 +9832,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129895634</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>57741</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,37 +9843,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457704</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678154</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9917,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 53931-2025 artfynd.xlsx
+++ b/artfynd/A 53931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7189845</v>
+        <v>7189860</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457848.6139825378</v>
+        <v>457849</v>
       </c>
       <c r="R2" t="n">
-        <v>6678213.076966906</v>
+        <v>6678213</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,21 +745,11 @@
           <t>2014-02-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-02-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +762,16 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>grov tallhögstubbe i skiktad granskog med björk</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov tallhögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -785,22 +782,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Via Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7189862</v>
+        <v>59906138</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +800,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor Mörttjärnen, Dlr</t>
+          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457886.0807821131</v>
+        <v>457784</v>
       </c>
       <c r="R3" t="n">
-        <v>6678183.341496453</v>
+        <v>6678038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,9 +881,34 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>granar i skiktad granskog med björk</t>
+          <t>skiktad drygt 125-årig granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # högstubbe 2,5 m hög, 50 cm grov, spår efter 2-3 bränder # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,22 +919,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7189860</v>
+        <v>129906105</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,36 +937,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457848.6139825378</v>
+        <v>458040</v>
       </c>
       <c r="R4" t="n">
-        <v>6678213.076966906</v>
+        <v>6678171</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,57 +991,42 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>grov tallhögstubbe i skiktad granskog med björk</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1043,12 +1036,7 @@
         <v>7189861</v>
       </c>
       <c r="B5" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457848.6139825378</v>
+        <v>457849</v>
       </c>
       <c r="R5" t="n">
-        <v>6678213.076966906</v>
+        <v>6678213</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,19 +1103,9 @@
           <t>2014-02-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-02-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,50 +1147,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7189842</v>
+        <v>59906108</v>
       </c>
       <c r="B6" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor Mörttjärnen, Dlr</t>
+          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457637.4714825568</v>
+        <v>457779</v>
       </c>
       <c r="R6" t="n">
-        <v>6678152.440888106</v>
+        <v>6678051</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,22 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,9 +1231,34 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>död tall i myr</t>
+          <t>skiktad drygt 125-årig granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # högstubbe 2,5 m hög, 25 cm grov # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1286,15 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7189853</v>
+        <v>129905534</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,34 +1287,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457981.6610655041</v>
+        <v>458192</v>
       </c>
       <c r="R7" t="n">
-        <v>6677885.716302157</v>
+        <v>6678014</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,22 +1341,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,36 +1367,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>granar i granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7189863</v>
+        <v>129896625</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,36 +1394,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor Mörttjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457763.7626142077</v>
+        <v>457943</v>
       </c>
       <c r="R8" t="n">
-        <v>6678146.012423921</v>
+        <v>6678019</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,22 +1448,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-02-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,36 +1474,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>granar i skiktad granskog med björk</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59906060</v>
+        <v>129901093</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,44 +1501,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457735.9358203876</v>
+        <v>457936</v>
       </c>
       <c r="R9" t="n">
-        <v>6678277.951300982</v>
+        <v>6678130</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,22 +1564,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,61 +1590,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>skiktad drygt 100-årig granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59906138</v>
+        <v>129901658</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,44 +1617,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457783.9075731969</v>
+        <v>457862</v>
       </c>
       <c r="R10" t="n">
-        <v>6678037.999083538</v>
+        <v>6678208</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1754,22 +1680,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,61 +1706,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>skiktad drygt 125-årig granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # högstubbe 2,5 m hög, 50 cm grov, spår efter 2-3 bränder # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>59906108</v>
+        <v>129901703</v>
       </c>
       <c r="B11" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,36 +1733,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457779.0822310741</v>
+        <v>457857</v>
       </c>
       <c r="R11" t="n">
-        <v>6678050.968793214</v>
+        <v>6678215</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1898,22 +1796,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,109 +1822,64 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>skiktad drygt 125-årig granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # högstubbe 2,5 m hög, 25 cm grov # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59906074</v>
+        <v>129895637</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457751.854875548</v>
+        <v>457691</v>
       </c>
       <c r="R12" t="n">
-        <v>6678191.844102954</v>
+        <v>6678174</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2050,22 +1903,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2076,98 +1929,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>skiktad drygt 100-årig granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # död gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>59906038</v>
+        <v>129896274</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457702.8961976252</v>
+        <v>458013</v>
       </c>
       <c r="R13" t="n">
-        <v>6678303.166454041</v>
+        <v>6677833</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2194,22 +2010,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-05-31</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2220,61 +2036,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>skiktad drygt 100-årig granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69622478</v>
+        <v>129895861</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2282,37 +2063,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457956.2193270365</v>
+        <v>457867</v>
       </c>
       <c r="R14" t="n">
-        <v>6678096.112019762</v>
+        <v>6677937</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2336,22 +2126,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mest troligt fjällig, intill gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2366,79 +2161,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100457887</v>
+        <v>7189852</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vansbro, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458089.6196789142</v>
+        <v>458214</v>
       </c>
       <c r="R15" t="n">
-        <v>6677971.897024486</v>
+        <v>6678135</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2462,22 +2238,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-05-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-05-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,34 +2255,34 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>död och levande gammal tall i blandbarrskog med tallöverståndare och gallrad för ca 20 år sedan</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896799</v>
+        <v>7189853</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2540,14 +2306,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457943</v>
+        <v>457982</v>
       </c>
       <c r="R16" t="n">
-        <v>6678103</v>
+        <v>6677886</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2574,27 +2340,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2605,66 +2356,68 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>granar i granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129895884</v>
+        <v>7189862</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457831</v>
+        <v>457886</v>
       </c>
       <c r="R17" t="n">
-        <v>6677903</v>
+        <v>6678183</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2691,27 +2444,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre och lite färskare ringhack på gran.</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2722,69 +2460,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>granar i skiktad granskog med björk</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Via Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129895608</v>
+        <v>7189863</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457684</v>
+        <v>457764</v>
       </c>
       <c r="R18" t="n">
-        <v>6678274</v>
+        <v>6678146</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2808,27 +2548,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:38</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2839,30 +2564,35 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>granar i skiktad granskog med björk</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Via Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129906213</v>
+        <v>59906038</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2884,19 +2614,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457973</v>
+        <v>457703</v>
       </c>
       <c r="R19" t="n">
-        <v>6678187</v>
+        <v>6678303</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,22 +2652,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2946,30 +2668,60 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>skiktad drygt 100-årig granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129903410</v>
+        <v>59906060</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2990,17 +2742,27 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457802</v>
+        <v>457736</v>
       </c>
       <c r="R20" t="n">
-        <v>6678361</v>
+        <v>6678278</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3027,22 +2789,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3053,66 +2805,101 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>skiktad drygt 100-årig granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896363</v>
+        <v>59906074</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Lagalammshöjden, Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458038</v>
+        <v>457752</v>
       </c>
       <c r="R21" t="n">
-        <v>6677894</v>
+        <v>6678192</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3139,22 +2926,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2016-05-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3165,69 +2942,94 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>skiktad drygt 100-årig granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # död gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129903311</v>
+        <v>69622478</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457721</v>
+        <v>457956</v>
       </c>
       <c r="R22" t="n">
-        <v>6678336</v>
+        <v>6678096</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3251,27 +3053,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,62 +3073,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129896298</v>
+        <v>129895673</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458013</v>
+        <v>457806</v>
       </c>
       <c r="R23" t="n">
-        <v>6677834</v>
+        <v>6678097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3373,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3383,19 +3165,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Barkfläk gran.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3415,14 +3192,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129906122</v>
+        <v>129895677</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3446,17 +3223,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458021</v>
+        <v>457806</v>
       </c>
       <c r="R24" t="n">
-        <v>6678149</v>
+        <v>6678096</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3485,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3495,12 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3527,14 +3299,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129903889</v>
+        <v>129895801</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3562,13 +3334,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458004</v>
+        <v>457826</v>
       </c>
       <c r="R25" t="n">
-        <v>6678076</v>
+        <v>6678001</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3597,7 +3369,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3607,7 +3379,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3634,54 +3406,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129901093</v>
+        <v>129895810</v>
       </c>
       <c r="B26" t="n">
-        <v>93010</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457936</v>
+        <v>457876</v>
       </c>
       <c r="R26" t="n">
-        <v>6678130</v>
+        <v>6677971</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3713,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3723,7 +3486,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,32 +3513,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129895637</v>
+        <v>129896383</v>
       </c>
       <c r="B27" t="n">
-        <v>91692</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,10 +3548,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457691</v>
+        <v>458001</v>
       </c>
       <c r="R27" t="n">
-        <v>6678174</v>
+        <v>6677916</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3820,7 +3583,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3830,7 +3593,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,14 +3620,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129906012</v>
+        <v>129896461</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3888,14 +3651,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458056</v>
+        <v>457943</v>
       </c>
       <c r="R28" t="n">
-        <v>6678145</v>
+        <v>6677964</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3927,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3700,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,14 +3727,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129903332</v>
+        <v>129896559</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3995,14 +3758,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457738</v>
+        <v>457931</v>
       </c>
       <c r="R29" t="n">
-        <v>6678344</v>
+        <v>6678011</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,7 +3797,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4044,7 +3807,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,14 +3834,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129904258</v>
+        <v>129896565</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4106,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458060</v>
+        <v>457928</v>
       </c>
       <c r="R30" t="n">
-        <v>6677965</v>
+        <v>6678006</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4151,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,45 +3941,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129905534</v>
+        <v>129896578</v>
       </c>
       <c r="B31" t="n">
-        <v>81165</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458192</v>
+        <v>457933</v>
       </c>
       <c r="R31" t="n">
-        <v>6678014</v>
+        <v>6678030</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4248,7 +4011,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4021,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt. På granstam.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4285,45 +4053,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129903137</v>
+        <v>129896775</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457711</v>
+        <v>457962</v>
       </c>
       <c r="R32" t="n">
-        <v>6678336</v>
+        <v>6678074</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4355,7 +4123,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4365,19 +4133,14 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4397,14 +4160,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129896809</v>
+        <v>129896799</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4432,10 +4195,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457924</v>
+        <v>457943</v>
       </c>
       <c r="R33" t="n">
-        <v>6678115</v>
+        <v>6678103</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4467,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4477,7 +4240,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4504,32 +4272,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129896625</v>
+        <v>129896809</v>
       </c>
       <c r="B34" t="n">
-        <v>91728</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4539,10 +4307,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457943</v>
+        <v>457924</v>
       </c>
       <c r="R34" t="n">
-        <v>6678019</v>
+        <v>6678115</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4574,7 +4342,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,7 +4352,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4611,53 +4379,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129895788</v>
+        <v>129900516</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457819</v>
+        <v>457915</v>
       </c>
       <c r="R35" t="n">
-        <v>6677981</v>
+        <v>6678101</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4686,7 +4449,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4696,12 +4459,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,50 +4486,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129901643</v>
+        <v>129901597</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457875</v>
+        <v>457892</v>
       </c>
       <c r="R36" t="n">
-        <v>6678186</v>
+        <v>6678150</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4803,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4813,12 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4845,14 +4593,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129905898</v>
+        <v>129901758</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4876,14 +4624,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458188</v>
+        <v>457814</v>
       </c>
       <c r="R37" t="n">
-        <v>6678089</v>
+        <v>6678274</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4915,7 +4663,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4925,7 +4673,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,14 +4700,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129903495</v>
+        <v>129901759</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4987,10 +4735,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457854</v>
+        <v>457813</v>
       </c>
       <c r="R38" t="n">
-        <v>6678241</v>
+        <v>6678274</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5022,7 +4770,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5032,7 +4780,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5059,14 +4807,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129896559</v>
+        <v>129901768</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5094,10 +4842,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457931</v>
+        <v>457765</v>
       </c>
       <c r="R39" t="n">
-        <v>6678011</v>
+        <v>6678299</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5129,7 +4877,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5139,7 +4887,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,50 +4914,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129896716</v>
+        <v>129903332</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457951</v>
+        <v>457738</v>
       </c>
       <c r="R40" t="n">
-        <v>6678037</v>
+        <v>6678344</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5241,7 +4984,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5251,12 +4994,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5283,54 +5021,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129901703</v>
+        <v>129903410</v>
       </c>
       <c r="B41" t="n">
-        <v>93010</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457857</v>
+        <v>457802</v>
       </c>
       <c r="R41" t="n">
-        <v>6678215</v>
+        <v>6678361</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5362,7 +5091,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5101,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,50 +5128,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129896531</v>
+        <v>129903495</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457940</v>
+        <v>457854</v>
       </c>
       <c r="R42" t="n">
-        <v>6677971</v>
+        <v>6678241</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5474,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5516,14 +5235,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129895810</v>
+        <v>129903740</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5551,10 +5270,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457876</v>
+        <v>457907</v>
       </c>
       <c r="R43" t="n">
-        <v>6677971</v>
+        <v>6678176</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5586,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5596,7 +5315,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5623,14 +5342,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129905906</v>
+        <v>129903770</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5654,14 +5373,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458187</v>
+        <v>457943</v>
       </c>
       <c r="R44" t="n">
-        <v>6678088</v>
+        <v>6678120</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5693,7 +5412,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5703,12 +5422,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 draperade tallar.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,50 +5449,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129895784</v>
+        <v>129903802</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457792</v>
+        <v>457983</v>
       </c>
       <c r="R45" t="n">
-        <v>6677984</v>
+        <v>6678105</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5519,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,12 +5529,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lite färskare ringhack tall.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5852,50 +5556,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129896481</v>
+        <v>129903889</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457943</v>
+        <v>458004</v>
       </c>
       <c r="R46" t="n">
-        <v>6677968</v>
+        <v>6678076</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5927,7 +5626,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5937,12 +5636,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5969,14 +5663,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129903770</v>
+        <v>129903924</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -6004,10 +5698,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457943</v>
+        <v>458007</v>
       </c>
       <c r="R47" t="n">
-        <v>6678120</v>
+        <v>6678050</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6039,7 +5733,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6049,7 +5743,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6076,50 +5770,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129903632</v>
+        <v>129904132</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457937</v>
+        <v>458061</v>
       </c>
       <c r="R48" t="n">
-        <v>6678255</v>
+        <v>6677989</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6151,7 +5840,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,12 +5850,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Inte jätte färska. På tall.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6193,50 +5877,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129901694</v>
+        <v>129904258</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457867</v>
+        <v>458060</v>
       </c>
       <c r="R49" t="n">
-        <v>6678204</v>
+        <v>6677965</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6268,7 +5947,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6278,19 +5957,14 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sparsamt ringhack på 2 tall.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -6310,53 +5984,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129895622</v>
+        <v>129905893</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457689</v>
+        <v>458190</v>
       </c>
       <c r="R50" t="n">
-        <v>6678248</v>
+        <v>6678079</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6385,7 +6054,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6395,12 +6064,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6427,45 +6091,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129904248</v>
+        <v>129905898</v>
       </c>
       <c r="B51" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458070</v>
+        <v>458188</v>
       </c>
       <c r="R51" t="n">
-        <v>6677915</v>
+        <v>6678089</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,7 +6161,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6507,7 +6171,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,45 +6198,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129904261</v>
+        <v>129905906</v>
       </c>
       <c r="B52" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458060</v>
+        <v>458187</v>
       </c>
       <c r="R52" t="n">
-        <v>6677965</v>
+        <v>6678088</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6604,7 +6268,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6614,7 +6278,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2 draperade tallar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6641,50 +6310,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129906281</v>
+        <v>129906012</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457937</v>
+        <v>458056</v>
       </c>
       <c r="R53" t="n">
-        <v>6678260</v>
+        <v>6678145</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6716,7 +6380,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6726,12 +6390,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6758,54 +6417,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129895861</v>
+        <v>129906122</v>
       </c>
       <c r="B54" t="n">
-        <v>93046</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457867</v>
+        <v>458021</v>
       </c>
       <c r="R54" t="n">
-        <v>6677937</v>
+        <v>6678149</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6837,7 +6487,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6847,12 +6497,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mest troligt fjällig, intill gran.</t>
+          <t>Hänglavsrikt.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6879,14 +6529,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129896461</v>
+        <v>129906213</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6910,14 +6560,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457943</v>
+        <v>457973</v>
       </c>
       <c r="R55" t="n">
-        <v>6677964</v>
+        <v>6678187</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6949,7 +6599,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6959,7 +6609,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6986,50 +6636,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129895750</v>
+        <v>129906347</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457776</v>
+        <v>457859</v>
       </c>
       <c r="R56" t="n">
-        <v>6677988</v>
+        <v>6678305</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7061,7 +6706,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7071,19 +6716,14 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, en rad med sav.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -7103,45 +6743,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129905893</v>
+        <v>7189842</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>79351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458190</v>
+        <v>457637</v>
       </c>
       <c r="R57" t="n">
-        <v>6678079</v>
+        <v>6678152</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7168,22 +6808,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7194,26 +6824,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>död tall i myr</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129903904</v>
+        <v>129903361</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,39 +6856,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458009</v>
+        <v>457778</v>
       </c>
       <c r="R58" t="n">
-        <v>6678073</v>
+        <v>6678373</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7285,7 +6915,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7295,12 +6925,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7327,10 +6952,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129896775</v>
+        <v>129904248</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7338,21 +6963,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7362,10 +6987,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457962</v>
+        <v>458070</v>
       </c>
       <c r="R59" t="n">
-        <v>6678074</v>
+        <v>6677915</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7397,7 +7022,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7407,7 +7032,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,10 +7059,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129904077</v>
+        <v>129904261</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7445,39 +7070,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458047</v>
+        <v>458060</v>
       </c>
       <c r="R60" t="n">
-        <v>6677984</v>
+        <v>6677965</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7509,7 +7129,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7519,12 +7139,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7551,10 +7166,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129901759</v>
+        <v>129905984</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7562,34 +7177,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457813</v>
+        <v>458114</v>
       </c>
       <c r="R61" t="n">
-        <v>6678274</v>
+        <v>6678116</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7621,7 +7236,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7631,7 +7246,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7658,10 +7273,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129895673</v>
+        <v>7189845</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7669,37 +7284,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Stor Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457806</v>
+        <v>457849</v>
       </c>
       <c r="R62" t="n">
-        <v>6678097</v>
+        <v>6678213</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7723,22 +7338,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:54</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:54</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7749,26 +7354,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>grov tallhögstubbe i skiktad granskog med björk</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129896652</v>
+        <v>100457887</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7776,42 +7386,51 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Vansbro, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457954</v>
+        <v>458090</v>
       </c>
       <c r="R63" t="n">
-        <v>6678018</v>
+        <v>6677972</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7454,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7866,61 +7480,71 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129903802</v>
+        <v>129896363</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457983</v>
+        <v>458038</v>
       </c>
       <c r="R64" t="n">
-        <v>6678105</v>
+        <v>6677894</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,7 +7576,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7586,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,10 +7613,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129903740</v>
+        <v>129895578</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8000,37 +7624,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457907</v>
+        <v>457678</v>
       </c>
       <c r="R65" t="n">
-        <v>6678176</v>
+        <v>6678274</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,7 +7688,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8069,7 +7698,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,10 +7730,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129906347</v>
+        <v>129895608</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8107,37 +7741,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457859</v>
+        <v>457684</v>
       </c>
       <c r="R66" t="n">
-        <v>6678305</v>
+        <v>6678274</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8166,7 +7805,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8176,7 +7815,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8203,10 +7847,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129895578</v>
+        <v>129895622</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8243,10 +7887,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457678</v>
+        <v>457689</v>
       </c>
       <c r="R67" t="n">
-        <v>6678274</v>
+        <v>6678248</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,7 +7922,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8288,7 +7932,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8320,45 +7964,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129896274</v>
+        <v>129895634</v>
       </c>
       <c r="B68" t="n">
-        <v>91692</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458013</v>
+        <v>457704</v>
       </c>
       <c r="R68" t="n">
-        <v>6677833</v>
+        <v>6678154</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8390,7 +8039,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8400,7 +8049,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8427,10 +8081,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129895677</v>
+        <v>129895750</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8438,37 +8092,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457806</v>
+        <v>457776</v>
       </c>
       <c r="R69" t="n">
-        <v>6678096</v>
+        <v>6677988</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8497,7 +8156,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8507,14 +8166,19 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, en rad med sav.</t>
         </is>
       </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG69" t="b">
         <v>0</v>
@@ -8534,10 +8198,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129901758</v>
+        <v>129895784</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8545,34 +8209,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457814</v>
+        <v>457792</v>
       </c>
       <c r="R70" t="n">
-        <v>6678274</v>
+        <v>6677984</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8604,7 +8273,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8614,7 +8283,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite färskare ringhack tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8641,10 +8315,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129904132</v>
+        <v>129895788</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8652,37 +8326,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458061</v>
+        <v>457819</v>
       </c>
       <c r="R71" t="n">
-        <v>6677989</v>
+        <v>6677981</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8711,7 +8390,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8400,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8748,10 +8432,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129896565</v>
+        <v>129895884</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8759,34 +8443,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457928</v>
+        <v>457831</v>
       </c>
       <c r="R72" t="n">
-        <v>6678006</v>
+        <v>6677903</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8818,7 +8507,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8517,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre och lite färskare ringhack på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8855,10 +8549,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129900516</v>
+        <v>129896298</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8866,37 +8560,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457915</v>
+        <v>458013</v>
       </c>
       <c r="R73" t="n">
-        <v>6678101</v>
+        <v>6677834</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8925,7 +8624,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8935,14 +8634,19 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Barkfläk gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG73" t="b">
         <v>0</v>
@@ -8962,10 +8666,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129901768</v>
+        <v>129896481</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8973,34 +8677,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457765</v>
+        <v>457943</v>
       </c>
       <c r="R74" t="n">
-        <v>6678299</v>
+        <v>6677968</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9032,7 +8741,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9042,7 +8751,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9069,10 +8783,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129895801</v>
+        <v>129896531</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9080,37 +8794,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457826</v>
+        <v>457940</v>
       </c>
       <c r="R75" t="n">
-        <v>6678001</v>
+        <v>6677971</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9139,7 +8858,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9149,7 +8868,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,10 +8900,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129901597</v>
+        <v>129896652</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,34 +8911,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457892</v>
+        <v>457954</v>
       </c>
       <c r="R76" t="n">
-        <v>6678150</v>
+        <v>6678018</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9246,7 +8975,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9256,7 +8985,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9283,42 +9017,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129901658</v>
+        <v>129896716</v>
       </c>
       <c r="B77" t="n">
-        <v>93010</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9327,10 +9057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457862</v>
+        <v>457951</v>
       </c>
       <c r="R77" t="n">
-        <v>6678208</v>
+        <v>6678037</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9362,7 +9092,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9372,7 +9102,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9399,10 +9134,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129906105</v>
+        <v>129901643</v>
       </c>
       <c r="B78" t="n">
-        <v>89124</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9410,34 +9145,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458040</v>
+        <v>457875</v>
       </c>
       <c r="R78" t="n">
-        <v>6678171</v>
+        <v>6678186</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9469,7 +9209,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9479,14 +9219,19 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -9506,10 +9251,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129896383</v>
+        <v>129901694</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9517,37 +9262,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458001</v>
+        <v>457867</v>
       </c>
       <c r="R79" t="n">
-        <v>6677916</v>
+        <v>6678204</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9576,7 +9326,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9586,14 +9336,19 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Sparsamt ringhack på 2 tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -9613,10 +9368,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129896578</v>
+        <v>129903137</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,34 +9379,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457933</v>
+        <v>457711</v>
       </c>
       <c r="R80" t="n">
-        <v>6678030</v>
+        <v>6678336</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9683,7 +9438,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9693,19 +9448,19 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Hänglavsrikt. På granstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG80" t="b">
         <v>0</v>
@@ -9725,10 +9480,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129895634</v>
+        <v>129903311</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9756,22 +9511,22 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Mörtbäcken, Mörtbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457704</v>
+        <v>457721</v>
       </c>
       <c r="R81" t="n">
-        <v>6678154</v>
+        <v>6678336</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9800,7 +9555,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9810,12 +9565,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9842,10 +9597,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129903924</v>
+        <v>129903632</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9853,34 +9608,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458007</v>
+        <v>457937</v>
       </c>
       <c r="R82" t="n">
-        <v>6678050</v>
+        <v>6678255</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9912,7 +9672,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9922,7 +9682,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Inte jätte färska. På tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9946,6 +9711,476 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129903904</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>458009</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6678073</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129904077</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>458047</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6677984</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129906281</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kalvtjärnen, Kalvtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>457937</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6678260</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129901750</v>
+      </c>
+      <c r="B86" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>457816</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6678266</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
